--- a/data/data_germany.xlsx
+++ b/data/data_germany.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6468b3e9d8abaf9d/MQDE/S2/ESSD/Projet/ESSD/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timotheedangleterre/Desktop/ENSAE/Semestre 1/ESSD/ProjetESSD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{BC4E3D7B-7CB6-484B-AA0A-1C140E9CC25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{250B42DA-E537-4C3A-B666-FA2BA1B441DA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C5933B-83BE-8B44-B7CF-46063A6880B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22965" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{6454D7D1-463C-084D-BBBF-FAC872F6478C}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16480" activeTab="1" xr2:uid="{6454D7D1-463C-084D-BBBF-FAC872F6478C}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenues" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,6 @@
     <author>tc={08293AAB-8FA5-2549-B0B1-6D2D0BD4FBF1}</author>
     <author>tc={C5AF9A64-618F-AD4F-8C58-7016077F8CC9}</author>
     <author>tc={DC113A1A-1CD2-374B-8249-EC8B7164FE3E}</author>
-    <author>tc={FCF09841-871C-444D-83E4-DB86CBF85ADC}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{BD513221-E624-1D4D-9409-BF2E9AA36BE2}">
@@ -122,14 +121,6 @@
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     Yahoo finance log returns</t>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="8" shapeId="0" xr:uid="{FCF09841-871C-444D-83E4-DB86CBF85ADC}">
-      <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    CSCICP02DEM460S</t>
       </text>
     </comment>
   </commentList>
@@ -260,7 +251,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="31">
   <si>
     <t>Dates</t>
   </si>
@@ -293,9 +284,6 @@
   </si>
   <si>
     <t xml:space="preserve">Stock market </t>
-  </si>
-  <si>
-    <t>Consumer confidence</t>
   </si>
   <si>
     <t>10y yield</t>
@@ -899,9 +887,6 @@
   <threadedComment ref="O1" dT="2026-02-09T16:46:20.14" personId="{8070DB0D-106F-D647-BD1B-7EB737D9DE56}" id="{DC113A1A-1CD2-374B-8249-EC8B7164FE3E}">
     <text>Yahoo finance log returns</text>
   </threadedComment>
-  <threadedComment ref="P1" dT="2026-02-09T16:16:35.84" personId="{8070DB0D-106F-D647-BD1B-7EB737D9DE56}" id="{FCF09841-871C-444D-83E4-DB86CBF85ADC}">
-    <text>CSCICP02DEM460S</text>
-  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -994,19 +979,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{333D1E4C-FF7B-C64F-AF43-B60AE776B9DE}">
-  <dimension ref="A1:P313"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:O313"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1" s="11" t="s">
         <v>1</v>
@@ -1015,7 +1000,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>3</v>
@@ -1024,7 +1009,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I1" s="11" t="s">
         <v>5</v>
@@ -1033,7 +1018,7 @@
         <v>6</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L1" s="11" t="s">
         <v>7</v>
@@ -1047,11 +1032,8 @@
       <c r="O1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>36526</v>
       </c>
@@ -1094,11 +1076,8 @@
       <c r="O2" s="8">
         <v>0.111848686020997</v>
       </c>
-      <c r="P2" s="2">
-        <v>-5.6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>36557</v>
       </c>
@@ -1141,11 +1120,8 @@
       <c r="O3" s="8">
         <v>-5.9249511941494902E-3</v>
       </c>
-      <c r="P3" s="2">
-        <v>-4.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>36586</v>
       </c>
@@ -1188,11 +1164,8 @@
       <c r="O4" s="8">
         <v>-2.4606156303372401E-2</v>
       </c>
-      <c r="P4" s="2">
-        <v>-4.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>36617</v>
       </c>
@@ -1235,11 +1208,8 @@
       <c r="O5" s="8">
         <v>-4.20060243531672E-2</v>
       </c>
-      <c r="P5" s="2">
-        <v>-5.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>36647</v>
       </c>
@@ -1282,11 +1252,8 @@
       <c r="O6" s="8">
         <v>-3.01938662519508E-2</v>
       </c>
-      <c r="P6" s="2">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>36678</v>
       </c>
@@ -1329,11 +1296,8 @@
       <c r="O7" s="8">
         <v>4.14806950729769E-2</v>
       </c>
-      <c r="P7" s="2">
-        <v>-5.9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>36708</v>
       </c>
@@ -1376,11 +1340,8 @@
       <c r="O8" s="8">
         <v>3.62052223152887E-3</v>
       </c>
-      <c r="P8" s="2">
-        <v>-3.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>36739</v>
       </c>
@@ -1423,11 +1384,8 @@
       <c r="O9" s="8">
         <v>-5.9717048692890601E-2</v>
       </c>
-      <c r="P9" s="2">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>36770</v>
       </c>
@@ -1470,11 +1428,8 @@
       <c r="O10" s="8">
         <v>4.0266131512263201E-2</v>
       </c>
-      <c r="P10" s="2">
-        <v>-6.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>36800</v>
       </c>
@@ -1517,11 +1472,8 @@
       <c r="O11" s="8">
         <v>-0.104947060075228</v>
       </c>
-      <c r="P11" s="2">
-        <v>-7.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>36831</v>
       </c>
@@ -1564,11 +1516,8 @@
       <c r="O12" s="8">
         <v>9.5705982046307998E-3</v>
       </c>
-      <c r="P12" s="2">
-        <v>-5.4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>36861</v>
       </c>
@@ -1611,11 +1560,8 @@
       <c r="O13" s="8">
         <v>5.4671880647104501E-2</v>
       </c>
-      <c r="P13" s="2">
-        <v>-5.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>36892</v>
       </c>
@@ -1658,11 +1604,8 @@
       <c r="O14" s="8">
         <v>-9.0330191216073899E-2</v>
       </c>
-      <c r="P14" s="2">
-        <v>-4.3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>36923</v>
       </c>
@@ -1705,11 +1648,8 @@
       <c r="O15" s="8">
         <v>-6.2869022181839498E-2</v>
       </c>
-      <c r="P15" s="2">
-        <v>-5.6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>36951</v>
       </c>
@@ -1752,11 +1692,8 @@
       <c r="O16" s="8">
         <v>7.1891878087779304E-2</v>
       </c>
-      <c r="P16" s="2">
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>36982</v>
       </c>
@@ -1799,11 +1736,8 @@
       <c r="O17" s="8">
         <v>-2.2805739422519601E-2</v>
       </c>
-      <c r="P17" s="2">
-        <v>-5.4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>37012</v>
       </c>
@@ -1846,11 +1780,8 @@
       <c r="O18" s="8">
         <v>-1.06521778957784E-2</v>
       </c>
-      <c r="P18" s="2">
-        <v>-7.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>37043</v>
       </c>
@@ -1893,11 +1824,8 @@
       <c r="O19" s="8">
         <v>-3.3089773619234798E-2</v>
       </c>
-      <c r="P19" s="2">
-        <v>-10.4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>37073</v>
       </c>
@@ -1940,11 +1868,8 @@
       <c r="O20" s="8">
         <v>-0.12197162586308399</v>
       </c>
-      <c r="P20" s="2">
-        <v>-10.7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>37104</v>
       </c>
@@ -1987,11 +1912,8 @@
       <c r="O21" s="8">
         <v>-0.18587246382334</v>
       </c>
-      <c r="P21" s="2">
-        <v>-12.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>37135</v>
       </c>
@@ -2034,11 +1956,8 @@
       <c r="O22" s="8">
         <v>5.6623235184378701E-2</v>
       </c>
-      <c r="P22" s="2">
-        <v>-11.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>37165</v>
       </c>
@@ -2081,11 +2000,8 @@
       <c r="O23" s="8">
         <v>9.0286114695754094E-2</v>
       </c>
-      <c r="P23" s="2">
-        <v>-11.4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>37196</v>
       </c>
@@ -2128,11 +2044,8 @@
       <c r="O24" s="8">
         <v>3.35380732340873E-2</v>
       </c>
-      <c r="P24" s="2">
-        <v>-13.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>37226</v>
       </c>
@@ -2175,11 +2088,8 @@
       <c r="O25" s="8">
         <v>-1.02244204103847E-2</v>
       </c>
-      <c r="P25" s="2">
-        <v>-13.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>37257</v>
       </c>
@@ -2222,11 +2132,8 @@
       <c r="O26" s="8">
         <v>-1.35080164233585E-2</v>
       </c>
-      <c r="P26" s="2">
-        <v>-14.7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>37288</v>
       </c>
@@ -2269,11 +2176,8 @@
       <c r="O27" s="8">
         <v>6.8673441743852606E-2</v>
       </c>
-      <c r="P27" s="2">
-        <v>-15.4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>37316</v>
       </c>
@@ -2316,11 +2220,8 @@
       <c r="O28" s="8">
         <v>-6.8252795261562596E-2</v>
       </c>
-      <c r="P28" s="2">
-        <v>-14.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>37347</v>
       </c>
@@ -2363,11 +2264,8 @@
       <c r="O29" s="8">
         <v>-4.5223059505193702E-2</v>
       </c>
-      <c r="P29" s="2">
-        <v>-15.6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>37377</v>
       </c>
@@ -2410,11 +2308,8 @@
       <c r="O30" s="8">
         <v>-9.4788086314228095E-2</v>
       </c>
-      <c r="P30" s="2">
-        <v>-15.7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>37408</v>
       </c>
@@ -2457,11 +2352,8 @@
       <c r="O31" s="8">
         <v>-0.16926241416469001</v>
       </c>
-      <c r="P31" s="2">
-        <v>-16.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>37438</v>
       </c>
@@ -2504,11 +2396,8 @@
       <c r="O32" s="8">
         <v>3.4533721032712402E-3</v>
       </c>
-      <c r="P32" s="2">
-        <v>-14.6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>37469</v>
       </c>
@@ -2551,11 +2440,8 @@
       <c r="O33" s="8">
         <v>-0.293326910897099</v>
       </c>
-      <c r="P33" s="2">
-        <v>-16.3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>37500</v>
       </c>
@@ -2598,11 +2484,8 @@
       <c r="O34" s="8">
         <v>0.12980974771940601</v>
       </c>
-      <c r="P34" s="2">
-        <v>-15.1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>37530</v>
       </c>
@@ -2645,11 +2528,8 @@
       <c r="O35" s="8">
         <v>5.1754347748044403E-2</v>
       </c>
-      <c r="P35" s="2">
-        <v>-18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>37561</v>
       </c>
@@ -2692,11 +2572,8 @@
       <c r="O36" s="8">
         <v>-0.13789510203043201</v>
       </c>
-      <c r="P36" s="2">
-        <v>-24.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>37591</v>
       </c>
@@ -2739,11 +2616,8 @@
       <c r="O37" s="8">
         <v>-5.13545446787287E-2</v>
       </c>
-      <c r="P37" s="2">
-        <v>-25.8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>37622</v>
       </c>
@@ -2786,11 +2660,8 @@
       <c r="O38" s="8">
         <v>-7.58756917913503E-2</v>
       </c>
-      <c r="P38" s="2">
-        <v>-23.2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>37653</v>
       </c>
@@ -2833,11 +2704,8 @@
       <c r="O39" s="8">
         <v>-4.9570361160313298E-2</v>
       </c>
-      <c r="P39" s="2">
-        <v>-24.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>37681</v>
       </c>
@@ -2880,11 +2748,8 @@
       <c r="O40" s="8">
         <v>0.193737746804094</v>
       </c>
-      <c r="P40" s="2">
-        <v>-23.4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>37712</v>
       </c>
@@ -2927,11 +2792,8 @@
       <c r="O41" s="8">
         <v>1.3718970746455599E-2</v>
       </c>
-      <c r="P41" s="2">
-        <v>-21.7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>37742</v>
       </c>
@@ -2974,11 +2836,8 @@
       <c r="O42" s="8">
         <v>7.6739289513859901E-2</v>
       </c>
-      <c r="P42" s="2">
-        <v>-20.9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>37773</v>
       </c>
@@ -3021,11 +2880,8 @@
       <c r="O43" s="8">
         <v>7.9726906607758594E-2</v>
       </c>
-      <c r="P43" s="2">
-        <v>-18.8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>37803</v>
       </c>
@@ -3068,11 +2924,8 @@
       <c r="O44" s="8">
         <v>-9.4085555459777503E-4</v>
       </c>
-      <c r="P44" s="2">
-        <v>-15.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>37834</v>
       </c>
@@ -3115,11 +2968,8 @@
       <c r="O45" s="8">
         <v>-6.7608556684577395E-2</v>
       </c>
-      <c r="P45" s="2">
-        <v>-18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>37865</v>
       </c>
@@ -3162,11 +3012,8 @@
       <c r="O46" s="8">
         <v>0.115627929501139</v>
       </c>
-      <c r="P46" s="2">
-        <v>-18.3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>37895</v>
       </c>
@@ -3209,11 +3056,8 @@
       <c r="O47" s="8">
         <v>2.4308327639889899E-2</v>
       </c>
-      <c r="P47" s="2">
-        <v>-18</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>37926</v>
       </c>
@@ -3256,11 +3100,8 @@
       <c r="O48" s="8">
         <v>5.6870941869297198E-2</v>
       </c>
-      <c r="P48" s="2">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>37956</v>
       </c>
@@ -3303,11 +3144,8 @@
       <c r="O49" s="8">
         <v>2.3291925425830601E-2</v>
       </c>
-      <c r="P49" s="2">
-        <v>-17.7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>37987</v>
       </c>
@@ -3350,11 +3188,8 @@
       <c r="O50" s="8">
         <v>-1.0014046089356301E-2</v>
       </c>
-      <c r="P50" s="2">
-        <v>-19.600000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>38018</v>
       </c>
@@ -3397,11 +3232,8 @@
       <c r="O51" s="8">
         <v>-4.1012181651057099E-2</v>
       </c>
-      <c r="P51" s="2">
-        <v>-16.2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>38047</v>
       </c>
@@ -3444,11 +3276,8 @@
       <c r="O52" s="8">
         <v>3.2778115786023E-2</v>
       </c>
-      <c r="P52" s="2">
-        <v>-17.3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>38078</v>
       </c>
@@ -3491,11 +3320,8 @@
       <c r="O53" s="8">
         <v>-1.6138738075330401E-2</v>
       </c>
-      <c r="P53" s="2">
-        <v>-17.8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>38108</v>
       </c>
@@ -3538,11 +3364,8 @@
       <c r="O54" s="8">
         <v>3.2939462694782803E-2</v>
       </c>
-      <c r="P54" s="2">
-        <v>-18.3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>38139</v>
       </c>
@@ -3585,11 +3408,8 @@
       <c r="O55" s="8">
         <v>-3.9540417611966902E-2</v>
       </c>
-      <c r="P55" s="2">
-        <v>-17.100000000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>38169</v>
       </c>
@@ -3632,11 +3452,8 @@
       <c r="O56" s="8">
         <v>-2.87489484783769E-2</v>
       </c>
-      <c r="P56" s="2">
-        <v>-18.100000000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>38200</v>
       </c>
@@ -3679,11 +3496,8 @@
       <c r="O57" s="8">
         <v>2.80529988849079E-2</v>
       </c>
-      <c r="P57" s="2">
-        <v>-17.7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>38231</v>
       </c>
@@ -3726,11 +3540,8 @@
       <c r="O58" s="8">
         <v>1.7152798504905999E-2</v>
       </c>
-      <c r="P58" s="2">
-        <v>-15.8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>38261</v>
       </c>
@@ -3773,11 +3584,8 @@
       <c r="O59" s="8">
         <v>4.1001260062236297E-2</v>
       </c>
-      <c r="P59" s="2">
-        <v>-17.399999999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>38292</v>
       </c>
@@ -3820,11 +3628,8 @@
       <c r="O60" s="8">
         <v>3.10401525621966E-2</v>
       </c>
-      <c r="P60" s="2">
-        <v>-17.7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>38322</v>
       </c>
@@ -3867,11 +3672,8 @@
       <c r="O61" s="8">
         <v>-2.8903549950776202E-4</v>
       </c>
-      <c r="P61" s="2">
-        <v>-16.7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>38353</v>
       </c>
@@ -3914,11 +3716,8 @@
       <c r="O62" s="8">
         <v>2.22290045964222E-2</v>
       </c>
-      <c r="P62" s="2">
-        <v>-13.7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>38384</v>
       </c>
@@ -3961,11 +3760,8 @@
       <c r="O63" s="8">
         <v>-3.95485320812128E-4</v>
       </c>
-      <c r="P63" s="2">
-        <v>-14.5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>38412</v>
       </c>
@@ -4008,11 +3804,8 @@
       <c r="O64" s="8">
         <v>-3.8424616894092302E-2</v>
       </c>
-      <c r="P64" s="2">
-        <v>-15.2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>38443</v>
       </c>
@@ -4055,11 +3848,8 @@
       <c r="O65" s="8">
         <v>6.3821551296939602E-2</v>
       </c>
-      <c r="P65" s="2">
-        <v>-15.4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>38473</v>
       </c>
@@ -4102,11 +3892,8 @@
       <c r="O66" s="8">
         <v>2.7779205722774598E-2</v>
       </c>
-      <c r="P66" s="2">
-        <v>-14.7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>38504</v>
       </c>
@@ -4149,11 +3936,8 @@
       <c r="O67" s="8">
         <v>6.3407109683772903E-2</v>
       </c>
-      <c r="P67" s="2">
-        <v>-15.2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>38534</v>
       </c>
@@ -4196,11 +3980,8 @@
       <c r="O68" s="8">
         <v>-1.16940295186438E-2</v>
       </c>
-      <c r="P68" s="2">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>38565</v>
       </c>
@@ -4243,11 +4024,8 @@
       <c r="O69" s="8">
         <v>4.3440960416413398E-2</v>
       </c>
-      <c r="P69" s="2">
-        <v>-14.3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>38596</v>
       </c>
@@ -4290,11 +4068,8 @@
       <c r="O70" s="8">
         <v>-2.30729380706549E-2</v>
       </c>
-      <c r="P70" s="2">
-        <v>-13.9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>38626</v>
       </c>
@@ -4337,11 +4112,8 @@
       <c r="O71" s="8">
         <v>5.2238276234790597E-2</v>
       </c>
-      <c r="P71" s="2">
-        <v>-12.7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>38657</v>
       </c>
@@ -4384,11 +4156,8 @@
       <c r="O72" s="8">
         <v>4.05388013129322E-2</v>
       </c>
-      <c r="P72" s="2">
-        <v>-13.1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>38687</v>
       </c>
@@ -4431,11 +4200,8 @@
       <c r="O73" s="8">
         <v>4.7993384031359602E-2</v>
       </c>
-      <c r="P73" s="2">
-        <v>-11.7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>38718</v>
       </c>
@@ -4478,11 +4244,8 @@
       <c r="O74" s="8">
         <v>2.12541772824348E-2</v>
       </c>
-      <c r="P74" s="2">
-        <v>-7.4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>38749</v>
       </c>
@@ -4525,11 +4288,8 @@
       <c r="O75" s="8">
         <v>2.9585408250438799E-2</v>
       </c>
-      <c r="P75" s="2">
-        <v>-8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>38777</v>
       </c>
@@ -4572,11 +4332,8 @@
       <c r="O76" s="8">
         <v>6.6461275641351803E-3</v>
       </c>
-      <c r="P76" s="2">
-        <v>-8.6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>38808</v>
       </c>
@@ -4619,11 +4376,8 @@
       <c r="O77" s="8">
         <v>-5.4193734252946199E-2</v>
       </c>
-      <c r="P77" s="2">
-        <v>-8.3000000000000007</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>38838</v>
       </c>
@@ -4666,11 +4420,8 @@
       <c r="O78" s="8">
         <v>-1.6789142560789099E-3</v>
       </c>
-      <c r="P78" s="2">
-        <v>-5.9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>38869</v>
       </c>
@@ -4713,11 +4464,8 @@
       <c r="O79" s="8">
         <v>-2.3577839243316099E-4</v>
       </c>
-      <c r="P79" s="2">
-        <v>-7.4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>38899</v>
       </c>
@@ -4760,11 +4508,8 @@
       <c r="O80" s="8">
         <v>3.0778150659468699E-2</v>
       </c>
-      <c r="P80" s="2">
-        <v>-8.5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>38930</v>
       </c>
@@ -4807,11 +4552,8 @@
       <c r="O81" s="8">
         <v>2.4404696572020199E-2</v>
       </c>
-      <c r="P81" s="2">
-        <v>-9</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>38961</v>
       </c>
@@ -4854,11 +4596,8 @@
       <c r="O82" s="8">
         <v>4.3123189912208197E-2</v>
       </c>
-      <c r="P82" s="2">
-        <v>-9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>38991</v>
       </c>
@@ -4901,11 +4640,8 @@
       <c r="O83" s="8">
         <v>6.4032128136766201E-3</v>
       </c>
-      <c r="P83" s="2">
-        <v>-10.7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>39022</v>
       </c>
@@ -4948,11 +4684,8 @@
       <c r="O84" s="8">
         <v>4.4595570244412699E-2</v>
       </c>
-      <c r="P84" s="2">
-        <v>-9.6</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>39052</v>
       </c>
@@ -4995,11 +4728,8 @@
       <c r="O85" s="8">
         <v>2.8716976130818101E-2</v>
       </c>
-      <c r="P85" s="2">
-        <v>-8.1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>39083</v>
       </c>
@@ -5042,11 +4772,8 @@
       <c r="O86" s="8">
         <v>-1.0910493683644201E-2</v>
       </c>
-      <c r="P86" s="2">
-        <v>-7.7</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>39114</v>
       </c>
@@ -5089,11 +4816,8 @@
       <c r="O87" s="8">
         <v>2.9577111641844001E-2</v>
       </c>
-      <c r="P87" s="2">
-        <v>-5.4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>39142</v>
       </c>
@@ -5136,11 +4860,8 @@
       <c r="O88" s="8">
         <v>6.8691491180905104E-2</v>
       </c>
-      <c r="P88" s="2">
-        <v>-4.7</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>39173</v>
       </c>
@@ -5183,11 +4904,8 @@
       <c r="O89" s="8">
         <v>6.2035674360270597E-2</v>
       </c>
-      <c r="P89" s="2">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>39203</v>
       </c>
@@ -5230,11 +4948,8 @@
       <c r="O90" s="8">
         <v>1.5642480139463899E-2</v>
       </c>
-      <c r="P90" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>39234</v>
       </c>
@@ -5277,11 +4992,8 @@
       <c r="O91" s="8">
         <v>-5.4296858645066899E-2</v>
       </c>
-      <c r="P91" s="2">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>39264</v>
       </c>
@@ -5324,11 +5036,8 @@
       <c r="O92" s="8">
         <v>7.0987927379011504E-3</v>
       </c>
-      <c r="P92" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>39295</v>
       </c>
@@ -5371,11 +5080,8 @@
       <c r="O93" s="8">
         <v>2.8820634673508001E-2</v>
       </c>
-      <c r="P93" s="2">
-        <v>-4.2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>39326</v>
       </c>
@@ -5418,11 +5124,8 @@
       <c r="O94" s="8">
         <v>1.98625169456275E-2</v>
       </c>
-      <c r="P94" s="2">
-        <v>-5.8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>39356</v>
       </c>
@@ -5465,11 +5168,8 @@
       <c r="O95" s="8">
         <v>-1.8717050656217499E-2</v>
       </c>
-      <c r="P95" s="2">
-        <v>-5.7</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>39387</v>
       </c>
@@ -5512,11 +5212,8 @@
       <c r="O96" s="8">
         <v>2.4697174735417E-2</v>
       </c>
-      <c r="P96" s="2">
-        <v>-8.6</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>39417</v>
       </c>
@@ -5559,11 +5256,8 @@
       <c r="O97" s="8">
         <v>-0.16331721706246699</v>
       </c>
-      <c r="P97" s="2">
-        <v>-8.1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>39448</v>
       </c>
@@ -5606,11 +5300,8 @@
       <c r="O98" s="8">
         <v>-1.52386819990173E-2</v>
       </c>
-      <c r="P98" s="2">
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>39479</v>
       </c>
@@ -5653,11 +5344,8 @@
       <c r="O99" s="8">
         <v>-3.2097622823616903E-2</v>
       </c>
-      <c r="P99" s="2">
-        <v>-9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>39508</v>
       </c>
@@ -5700,11 +5388,8 @@
       <c r="O100" s="8">
         <v>6.14040464165004E-2</v>
       </c>
-      <c r="P100" s="2">
-        <v>-9.3000000000000007</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>39539</v>
       </c>
@@ -5747,11 +5432,8 @@
       <c r="O101" s="8">
         <v>2.10707389491969E-2</v>
       </c>
-      <c r="P101" s="2">
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>39569</v>
       </c>
@@ -5794,11 +5476,8 @@
       <c r="O102" s="8">
         <v>-0.100486200815029</v>
       </c>
-      <c r="P102" s="2">
-        <v>-10.3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>39600</v>
       </c>
@@ -5841,11 +5520,8 @@
       <c r="O103" s="8">
         <v>9.4962420404005599E-3</v>
       </c>
-      <c r="P103" s="2">
-        <v>-12.3</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>39630</v>
       </c>
@@ -5888,11 +5564,8 @@
       <c r="O104" s="8">
         <v>-8.8763372832740793E-3</v>
       </c>
-      <c r="P104" s="2">
-        <v>-15.8</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>39661</v>
       </c>
@@ -5935,11 +5608,8 @@
       <c r="O105" s="8">
         <v>-9.6584333056723495E-2</v>
       </c>
-      <c r="P105" s="2">
-        <v>-16.7</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>39692</v>
       </c>
@@ -5982,11 +5652,8 @@
       <c r="O106" s="8">
         <v>-0.15616288908964299</v>
       </c>
-      <c r="P106" s="2">
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>39722</v>
       </c>
@@ -6029,11 +5696,8 @@
       <c r="O107" s="8">
         <v>-6.5989918842177503E-2</v>
       </c>
-      <c r="P107" s="2">
-        <v>-18</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>39753</v>
       </c>
@@ -6076,11 +5740,8 @@
       <c r="O108" s="8">
         <v>2.9699566303380099E-2</v>
       </c>
-      <c r="P108" s="2">
-        <v>-17.600000000000001</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>39783</v>
       </c>
@@ -6123,11 +5784,8 @@
       <c r="O109" s="8">
         <v>-0.103244589896516</v>
       </c>
-      <c r="P109" s="2">
-        <v>-21</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>39814</v>
       </c>
@@ -6170,11 +5828,8 @@
       <c r="O110" s="8">
         <v>-0.121048265599494</v>
       </c>
-      <c r="P110" s="2">
-        <v>-20.6</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>39845</v>
       </c>
@@ -6217,11 +5872,8 @@
       <c r="O111" s="8">
         <v>6.0817129044151499E-2</v>
       </c>
-      <c r="P111" s="2">
-        <v>-20.8</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>39873</v>
       </c>
@@ -6264,11 +5916,8 @@
       <c r="O112" s="8">
         <v>0.154968057772958</v>
       </c>
-      <c r="P112" s="2">
-        <v>-22.4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>39904</v>
       </c>
@@ -6311,11 +5960,8 @@
       <c r="O113" s="8">
         <v>3.53002385304464E-2</v>
       </c>
-      <c r="P113" s="2">
-        <v>-20.6</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>39934</v>
       </c>
@@ -6358,11 +6004,8 @@
       <c r="O114" s="8">
         <v>-2.7116945463070901E-2</v>
       </c>
-      <c r="P114" s="2">
-        <v>-19.7</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>39965</v>
       </c>
@@ -6405,11 +6048,8 @@
       <c r="O115" s="8">
         <v>0.103338355889289</v>
       </c>
-      <c r="P115" s="2">
-        <v>-18.3</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>39995</v>
       </c>
@@ -6452,11 +6092,8 @@
       <c r="O116" s="8">
         <v>2.4540046666183798E-2</v>
       </c>
-      <c r="P116" s="2">
-        <v>-15.3</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>40026</v>
       </c>
@@ -6499,11 +6136,8 @@
       <c r="O117" s="8">
         <v>3.7806053492298403E-2</v>
       </c>
-      <c r="P117" s="2">
-        <v>-12.2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>40057</v>
       </c>
@@ -6546,11 +6180,8 @@
       <c r="O118" s="8">
         <v>-4.6933298011303699E-2</v>
       </c>
-      <c r="P118" s="2">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>40087</v>
       </c>
@@ -6593,11 +6224,8 @@
       <c r="O119" s="8">
         <v>3.8224371112022502E-2</v>
       </c>
-      <c r="P119" s="2">
-        <v>-8.6</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>40118</v>
       </c>
@@ -6640,11 +6268,8 @@
       <c r="O120" s="8">
         <v>5.7249352097251502E-2</v>
       </c>
-      <c r="P120" s="2">
-        <v>-10.9</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>40148</v>
       </c>
@@ -6687,11 +6312,8 @@
       <c r="O121" s="8">
         <v>-6.0304192571880598E-2</v>
       </c>
-      <c r="P121" s="2">
-        <v>-9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>40179</v>
       </c>
@@ -6734,11 +6356,8 @@
       <c r="O122" s="8">
         <v>-1.8434640166748999E-3</v>
       </c>
-      <c r="P122" s="2">
-        <v>-11.5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>40210</v>
       </c>
@@ -6781,11 +6400,8 @@
       <c r="O123" s="8">
         <v>9.4537566370185303E-2</v>
       </c>
-      <c r="P123" s="2">
-        <v>-11.5</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>40238</v>
       </c>
@@ -6828,11 +6444,8 @@
       <c r="O124" s="8">
         <v>-2.90491639881196E-3</v>
       </c>
-      <c r="P124" s="2">
-        <v>-9.5</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>40269</v>
       </c>
@@ -6875,11 +6488,8 @@
       <c r="O125" s="8">
         <v>-2.8327462453287201E-2</v>
       </c>
-      <c r="P125" s="2">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>40299</v>
       </c>
@@ -6922,11 +6532,8 @@
       <c r="O126" s="8">
         <v>1.99489750576376E-4</v>
       </c>
-      <c r="P126" s="2">
-        <v>-9.9</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>40330</v>
       </c>
@@ -6969,11 +6576,8 @@
       <c r="O127" s="8">
         <v>3.01257507613002E-2</v>
       </c>
-      <c r="P127" s="2">
-        <v>-9</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>40360</v>
       </c>
@@ -7016,11 +6620,8 @@
       <c r="O128" s="8">
         <v>-3.6904127581514998E-2</v>
       </c>
-      <c r="P128" s="2">
-        <v>-3.7</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>40391</v>
       </c>
@@ -7063,11 +6664,8 @@
       <c r="O129" s="8">
         <v>5.0001166797875002E-2</v>
       </c>
-      <c r="P129" s="2">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>40422</v>
       </c>
@@ -7110,11 +6708,8 @@
       <c r="O130" s="8">
         <v>5.8058200810457102E-2</v>
       </c>
-      <c r="P130" s="2">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>40452</v>
       </c>
@@ -7157,11 +6752,8 @@
       <c r="O131" s="8">
         <v>1.31109526893063E-2</v>
       </c>
-      <c r="P131" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>40483</v>
       </c>
@@ -7204,11 +6796,8 @@
       <c r="O132" s="8">
         <v>3.3187639431439202E-2</v>
       </c>
-      <c r="P132" s="2">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>40513</v>
       </c>
@@ -7251,11 +6840,8 @@
       <c r="O133" s="8">
         <v>2.33420962618727E-2</v>
       </c>
-      <c r="P133" s="2">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>40544</v>
       </c>
@@ -7298,11 +6884,8 @@
       <c r="O134" s="8">
         <v>2.7157426752474099E-2</v>
       </c>
-      <c r="P134" s="2">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>40575</v>
       </c>
@@ -7345,11 +6928,8 @@
       <c r="O135" s="8">
         <v>-3.22810954099957E-2</v>
       </c>
-      <c r="P135" s="2">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>40603</v>
       </c>
@@ -7392,11 +6972,8 @@
       <c r="O136" s="8">
         <v>6.5034918411234002E-2</v>
       </c>
-      <c r="P136" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>40634</v>
       </c>
@@ -7439,11 +7016,8 @@
       <c r="O137" s="8">
         <v>-2.9819576373086E-2</v>
       </c>
-      <c r="P137" s="2">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>40664</v>
       </c>
@@ -7486,11 +7060,8 @@
       <c r="O138" s="8">
         <v>1.1254472695887001E-2</v>
       </c>
-      <c r="P138" s="2">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>40695</v>
       </c>
@@ -7533,11 +7104,8 @@
       <c r="O139" s="8">
         <v>-2.9925874226060901E-2</v>
       </c>
-      <c r="P139" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>40725</v>
       </c>
@@ -7580,11 +7148,8 @@
       <c r="O140" s="8">
         <v>-0.21309573317035399</v>
       </c>
-      <c r="P140" s="2">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>40756</v>
       </c>
@@ -7627,11 +7192,8 @@
       <c r="O141" s="8">
         <v>-5.0127146976390001E-2</v>
       </c>
-      <c r="P141" s="2">
-        <v>-4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>40787</v>
       </c>
@@ -7674,11 +7236,8 @@
       <c r="O142" s="8">
         <v>0.109927632860542</v>
       </c>
-      <c r="P142" s="2">
-        <v>-3.9</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>40817</v>
       </c>
@@ -7721,11 +7280,8 @@
       <c r="O143" s="8">
         <v>-8.5853722212210198E-3</v>
       </c>
-      <c r="P143" s="2">
-        <v>-6.3</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>40848</v>
       </c>
@@ -7768,11 +7324,8 @@
       <c r="O144" s="8">
         <v>-3.1784894387906E-2</v>
       </c>
-      <c r="P144" s="2">
-        <v>-6.2</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>40878</v>
       </c>
@@ -7815,11 +7368,8 @@
       <c r="O145" s="8">
         <v>9.0787929760299604E-2</v>
       </c>
-      <c r="P145" s="2">
-        <v>-4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>40909</v>
       </c>
@@ -7862,11 +7412,8 @@
       <c r="O146" s="8">
         <v>5.96752641347056E-2</v>
       </c>
-      <c r="P146" s="2">
-        <v>-4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>40940</v>
       </c>
@@ -7909,11 +7456,8 @@
       <c r="O147" s="8">
         <v>1.3149590428955801E-2</v>
       </c>
-      <c r="P147" s="2">
-        <v>-4.5</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>40969</v>
       </c>
@@ -7956,11 +7500,8 @@
       <c r="O148" s="8">
         <v>-2.7086550263575801E-2</v>
       </c>
-      <c r="P148" s="2">
-        <v>-4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>41000</v>
       </c>
@@ -8003,11 +7544,8 @@
       <c r="O149" s="8">
         <v>-7.6319299145273703E-2</v>
       </c>
-      <c r="P149" s="2">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>41030</v>
       </c>
@@ -8050,11 +7588,8 @@
       <c r="O150" s="8">
         <v>2.39588747716333E-2</v>
       </c>
-      <c r="P150" s="2">
-        <v>-4.3</v>
-      </c>
-    </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>41061</v>
       </c>
@@ -8097,11 +7632,8 @@
       <c r="O151" s="8">
         <v>5.3996345284742703E-2</v>
       </c>
-      <c r="P151" s="2">
-        <v>-3.9</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>41091</v>
       </c>
@@ -8144,11 +7676,8 @@
       <c r="O152" s="8">
         <v>2.8893744541173699E-2</v>
       </c>
-      <c r="P152" s="2">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>41122</v>
       </c>
@@ -8191,11 +7720,8 @@
       <c r="O153" s="8">
         <v>3.4592989299461897E-2</v>
       </c>
-      <c r="P153" s="2">
-        <v>-6.8</v>
-      </c>
-    </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>41153</v>
       </c>
@@ -8238,11 +7764,8 @@
       <c r="O154" s="8">
         <v>6.1450296402370003E-3</v>
       </c>
-      <c r="P154" s="2">
-        <v>-7.9</v>
-      </c>
-    </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>41183</v>
       </c>
@@ -8285,11 +7808,8 @@
       <c r="O155" s="8">
         <v>1.9756381593703399E-2</v>
       </c>
-      <c r="P155" s="2">
-        <v>-7.7</v>
-      </c>
-    </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>41214</v>
       </c>
@@ -8332,11 +7852,8 @@
       <c r="O156" s="8">
         <v>2.7554233588855202E-2</v>
       </c>
-      <c r="P156" s="2">
-        <v>-6.9</v>
-      </c>
-    </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>41244</v>
       </c>
@@ -8379,11 +7896,8 @@
       <c r="O157" s="8">
         <v>2.1271271087686099E-2</v>
       </c>
-      <c r="P157" s="2">
-        <v>-7.3</v>
-      </c>
-    </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>41275</v>
       </c>
@@ -8426,11 +7940,8 @@
       <c r="O158" s="8">
         <v>-4.4271451052182399E-3</v>
       </c>
-      <c r="P158" s="2">
-        <v>-5.6</v>
-      </c>
-    </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>41306</v>
       </c>
@@ -8473,11 +7984,8 @@
       <c r="O159" s="8">
         <v>6.9009513620414999E-3</v>
       </c>
-      <c r="P159" s="2">
-        <v>-4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>41334</v>
       </c>
@@ -8520,11 +8028,8 @@
       <c r="O160" s="8">
         <v>1.50744151153557E-2</v>
       </c>
-      <c r="P160" s="2">
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>41365</v>
       </c>
@@ -8567,11 +8072,8 @@
       <c r="O161" s="8">
         <v>5.3525894907714602E-2</v>
       </c>
-      <c r="P161" s="2">
-        <v>-4.7</v>
-      </c>
-    </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>41395</v>
       </c>
@@ -8614,11 +8116,8 @@
       <c r="O162" s="8">
         <v>-4.7791556243044701E-2</v>
       </c>
-      <c r="P162" s="2">
-        <v>-4.7</v>
-      </c>
-    </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>41426</v>
       </c>
@@ -8661,11 +8160,8 @@
       <c r="O163" s="8">
         <v>3.90250697989281E-2</v>
       </c>
-      <c r="P163" s="2">
-        <v>-4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>41456</v>
       </c>
@@ -8708,11 +8204,8 @@
       <c r="O164" s="8">
         <v>-2.1103238979252498E-2</v>
       </c>
-      <c r="P164" s="2">
-        <v>-3.9</v>
-      </c>
-    </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>41487</v>
       </c>
@@ -8755,11 +8248,8 @@
       <c r="O165" s="8">
         <v>5.8858010903346497E-2</v>
       </c>
-      <c r="P165" s="2">
-        <v>-4.3</v>
-      </c>
-    </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>41518</v>
       </c>
@@ -8802,11 +8292,8 @@
       <c r="O166" s="8">
         <v>4.9875499288914299E-2</v>
       </c>
-      <c r="P166" s="2">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>41548</v>
       </c>
@@ -8849,11 +8336,8 @@
       <c r="O167" s="8">
         <v>4.0286966294466701E-2</v>
       </c>
-      <c r="P167" s="2">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>41579</v>
       </c>
@@ -8896,11 +8380,8 @@
       <c r="O168" s="8">
         <v>1.54939838815942E-2</v>
       </c>
-      <c r="P168" s="2">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>41609</v>
       </c>
@@ -8943,11 +8424,8 @@
       <c r="O169" s="8">
         <v>-2.6056341199826201E-2</v>
       </c>
-      <c r="P169" s="2">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>41640</v>
       </c>
@@ -8990,11 +8468,8 @@
       <c r="O170" s="8">
         <v>4.0598083124759703E-2</v>
       </c>
-      <c r="P170" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>41671</v>
       </c>
@@ -9037,11 +8512,8 @@
       <c r="O171" s="8">
         <v>-1.4149237607458801E-2</v>
       </c>
-      <c r="P171" s="2">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>41699</v>
       </c>
@@ -9084,11 +8556,8 @@
       <c r="O172" s="8">
         <v>4.9397214256607898E-3</v>
       </c>
-      <c r="P172" s="2">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>41730</v>
       </c>
@@ -9131,11 +8600,8 @@
       <c r="O173" s="8">
         <v>3.4796344239657301E-2</v>
       </c>
-      <c r="P173" s="2">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>41760</v>
       </c>
@@ -9178,11 +8644,8 @@
       <c r="O174" s="8">
         <v>-1.1144666830492899E-2</v>
       </c>
-      <c r="P174" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>41791</v>
       </c>
@@ -9225,11 +8688,8 @@
       <c r="O175" s="8">
         <v>-4.4246059091339197E-2</v>
       </c>
-      <c r="P175" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>41821</v>
       </c>
@@ -9272,11 +8732,8 @@
       <c r="O176" s="8">
         <v>6.6416828655899698E-3</v>
       </c>
-      <c r="P176" s="2">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>41852</v>
       </c>
@@ -9319,11 +8776,8 @@
       <c r="O177" s="8">
         <v>4.3599878355316001E-4</v>
       </c>
-      <c r="P177" s="2">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>41883</v>
       </c>
@@ -9366,11 +8820,8 @@
       <c r="O178" s="8">
         <v>-1.56833548136621E-2</v>
       </c>
-      <c r="P178" s="2">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>41913</v>
       </c>
@@ -9413,11 +8864,8 @@
       <c r="O179" s="8">
         <v>6.7768723717097898E-2</v>
       </c>
-      <c r="P179" s="2">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>41944</v>
       </c>
@@ -9460,11 +8908,8 @@
       <c r="O180" s="8">
         <v>-1.7719685913595701E-2</v>
       </c>
-      <c r="P180" s="2">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>41974</v>
       </c>
@@ -9507,11 +8952,8 @@
       <c r="O181" s="8">
         <v>8.6764256635232698E-2</v>
       </c>
-      <c r="P181" s="2">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>42005</v>
       </c>
@@ -9554,11 +8996,8 @@
       <c r="O182" s="8">
         <v>6.4046183917533001E-2</v>
       </c>
-      <c r="P182" s="2">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>42036</v>
       </c>
@@ -9601,11 +9040,8 @@
       <c r="O183" s="8">
         <v>4.8324522718719003E-2</v>
       </c>
-      <c r="P183" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>42064</v>
       </c>
@@ -9648,11 +9084,8 @@
       <c r="O184" s="8">
         <v>-4.37113158841669E-2</v>
       </c>
-      <c r="P184" s="2">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>42095</v>
       </c>
@@ -9695,11 +9128,8 @@
       <c r="O185" s="8">
         <v>-3.54725011116841E-3</v>
       </c>
-      <c r="P185" s="2">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>42125</v>
       </c>
@@ -9742,11 +9172,8 @@
       <c r="O186" s="8">
         <v>-4.1944964251854303E-2</v>
       </c>
-      <c r="P186" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>42156</v>
       </c>
@@ -9789,11 +9216,8 @@
       <c r="O187" s="8">
         <v>3.2718040351463501E-2</v>
       </c>
-      <c r="P187" s="2">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>42186</v>
       </c>
@@ -9836,11 +9260,8 @@
       <c r="O188" s="8">
         <v>-9.7397802390855007E-2</v>
       </c>
-      <c r="P188" s="2">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>42217</v>
       </c>
@@ -9883,11 +9304,8 @@
       <c r="O189" s="8">
         <v>-6.0160962650682499E-2</v>
       </c>
-      <c r="P189" s="2">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>42248</v>
       </c>
@@ -9930,11 +9348,8 @@
       <c r="O190" s="8">
         <v>0.116138710406931</v>
       </c>
-      <c r="P190" s="2">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>42278</v>
       </c>
@@ -9977,11 +9392,8 @@
       <c r="O191" s="8">
         <v>4.7875457776937601E-2</v>
       </c>
-      <c r="P191" s="2">
-        <v>-4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>42309</v>
       </c>
@@ -10024,11 +9436,8 @@
       <c r="O192" s="8">
         <v>-5.7798119798164301E-2</v>
       </c>
-      <c r="P192" s="2">
-        <v>-4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>42339</v>
       </c>
@@ -10071,11 +9480,8 @@
       <c r="O193" s="8">
         <v>-9.2065742891163496E-2</v>
       </c>
-      <c r="P193" s="2">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>42370</v>
       </c>
@@ -10118,11 +9524,8 @@
       <c r="O194" s="8">
         <v>-3.1382033864236498E-2</v>
       </c>
-      <c r="P194" s="2">
-        <v>-2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>42401</v>
       </c>
@@ -10165,11 +9568,8 @@
       <c r="O195" s="8">
         <v>4.8322596012733102E-2</v>
       </c>
-      <c r="P195" s="2">
-        <v>-2.6</v>
-      </c>
-    </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>42430</v>
       </c>
@@ -10212,11 +9612,8 @@
       <c r="O196" s="8">
         <v>7.3443841583866699E-3</v>
       </c>
-      <c r="P196" s="2">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>42461</v>
       </c>
@@ -10259,11 +9656,8 @@
       <c r="O197" s="8">
         <v>2.2045391335192101E-2</v>
       </c>
-      <c r="P197" s="2">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>42491</v>
       </c>
@@ -10306,11 +9700,8 @@
       <c r="O198" s="8">
         <v>-5.8448700832512301E-2</v>
       </c>
-      <c r="P198" s="2">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>42522</v>
       </c>
@@ -10353,11 +9744,8 @@
       <c r="O199" s="8">
         <v>6.5706877725263596E-2</v>
       </c>
-      <c r="P199" s="2">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>42552</v>
       </c>
@@ -10400,11 +9788,8 @@
       <c r="O200" s="8">
         <v>2.4386120792158301E-2</v>
       </c>
-      <c r="P200" s="2">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>42583</v>
       </c>
@@ -10447,11 +9832,8 @@
       <c r="O201" s="8">
         <v>-7.7399951300858296E-3</v>
       </c>
-      <c r="P201" s="2">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>42614</v>
       </c>
@@ -10494,11 +9876,8 @@
       <c r="O202" s="8">
         <v>1.4544081581430401E-2</v>
       </c>
-      <c r="P202" s="2">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>42644</v>
       </c>
@@ -10541,11 +9920,8 @@
       <c r="O203" s="8">
         <v>-2.3196069444981799E-3</v>
       </c>
-      <c r="P203" s="2">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>42675</v>
       </c>
@@ -10588,11 +9964,8 @@
       <c r="O204" s="8">
         <v>7.6050023049042195E-2</v>
       </c>
-      <c r="P204" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>42705</v>
       </c>
@@ -10635,11 +10008,8 @@
       <c r="O205" s="8">
         <v>4.7140450460680904E-3</v>
       </c>
-      <c r="P205" s="2">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>42736</v>
       </c>
@@ -10682,11 +10052,8 @@
       <c r="O206" s="8">
         <v>2.55986740488847E-2</v>
       </c>
-      <c r="P206" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>42767</v>
       </c>
@@ -10729,11 +10096,8 @@
       <c r="O207" s="8">
         <v>3.9633663532784497E-2</v>
       </c>
-      <c r="P207" s="2">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>42795</v>
       </c>
@@ -10776,11 +10140,8 @@
       <c r="O208" s="8">
         <v>1.0112021500111401E-2</v>
       </c>
-      <c r="P208" s="2">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>42826</v>
       </c>
@@ -10823,11 +10184,8 @@
       <c r="O209" s="8">
         <v>1.41342164371014E-2</v>
       </c>
-      <c r="P209" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>42856</v>
       </c>
@@ -10870,11 +10228,8 @@
       <c r="O210" s="8">
         <v>-2.3251838565112599E-2</v>
       </c>
-      <c r="P210" s="2">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>42887</v>
       </c>
@@ -10917,11 +10272,8 @@
       <c r="O211" s="8">
         <v>-1.6926884920629E-2</v>
       </c>
-      <c r="P211" s="2">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>42917</v>
       </c>
@@ -10964,11 +10316,8 @@
       <c r="O212" s="8">
         <v>-5.1634039015926404E-3</v>
       </c>
-      <c r="P212" s="2">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>42948</v>
       </c>
@@ -11011,11 +10360,8 @@
       <c r="O213" s="8">
         <v>6.21481709604765E-2</v>
       </c>
-      <c r="P213" s="2">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>42979</v>
       </c>
@@ -11058,11 +10404,8 @@
       <c r="O214" s="8">
         <v>3.0757151494398699E-2</v>
       </c>
-      <c r="P214" s="2">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>43009</v>
       </c>
@@ -11105,11 +10448,8 @@
       <c r="O215" s="8">
         <v>-1.5662189706576499E-2</v>
       </c>
-      <c r="P215" s="2">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>43040</v>
       </c>
@@ -11152,11 +10492,8 @@
       <c r="O216" s="8">
         <v>-8.1985177085393008E-3</v>
       </c>
-      <c r="P216" s="2">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>43070</v>
       </c>
@@ -11199,11 +10536,8 @@
       <c r="O217" s="8">
         <v>2.0825785770625799E-2</v>
       </c>
-      <c r="P217" s="2">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>43101</v>
       </c>
@@ -11246,11 +10580,8 @@
       <c r="O218" s="8">
         <v>-5.8836178729487501E-2</v>
       </c>
-      <c r="P218" s="2">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>43132</v>
       </c>
@@ -11293,11 +10624,8 @@
       <c r="O219" s="8">
         <v>-2.76481920609708E-2</v>
       </c>
-      <c r="P219" s="2">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>43160</v>
       </c>
@@ -11340,11 +10668,8 @@
       <c r="O220" s="8">
         <v>4.1722284476579198E-2</v>
       </c>
-      <c r="P220" s="2">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>43191</v>
       </c>
@@ -11387,11 +10712,8 @@
       <c r="O221" s="8">
         <v>-5.7268535689125599E-4</v>
       </c>
-      <c r="P221" s="2">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>43221</v>
       </c>
@@ -11434,11 +10756,8 @@
       <c r="O222" s="8">
         <v>-2.3997857696789599E-2</v>
       </c>
-      <c r="P222" s="2">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>43252</v>
       </c>
@@ -11481,11 +10800,8 @@
       <c r="O223" s="8">
         <v>3.9787817818036003E-2</v>
       </c>
-      <c r="P223" s="2">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>43282</v>
       </c>
@@ -11528,11 +10844,8 @@
       <c r="O224" s="8">
         <v>-3.5080923832737199E-2</v>
       </c>
-      <c r="P224" s="2">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>43313</v>
       </c>
@@ -11575,11 +10888,8 @@
       <c r="O225" s="8">
         <v>-9.5348414473441796E-3</v>
       </c>
-      <c r="P225" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>43344</v>
       </c>
@@ -11622,11 +10932,8 @@
       <c r="O226" s="8">
         <v>-6.7486782228227696E-2</v>
       </c>
-      <c r="P226" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>43374</v>
       </c>
@@ -11669,11 +10976,8 @@
       <c r="O227" s="8">
         <v>-1.67607205951796E-2</v>
       </c>
-      <c r="P227" s="2">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>43405</v>
       </c>
@@ -11716,11 +11020,8 @@
       <c r="O228" s="8">
         <v>-6.4036713152630001E-2</v>
       </c>
-      <c r="P228" s="2">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>43435</v>
       </c>
@@ -11763,11 +11064,8 @@
       <c r="O229" s="8">
         <v>5.6534283831409099E-2</v>
       </c>
-      <c r="P229" s="2">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>43466</v>
       </c>
@@ -11810,11 +11108,8 @@
       <c r="O230" s="8">
         <v>3.0197012166079101E-2</v>
       </c>
-      <c r="P230" s="2">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>43497</v>
       </c>
@@ -11857,11 +11152,8 @@
       <c r="O231" s="8">
         <v>9.0274593453010298E-4</v>
       </c>
-      <c r="P231" s="2">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>43525</v>
       </c>
@@ -11904,11 +11196,8 @@
       <c r="O232" s="8">
         <v>6.85677754379697E-2</v>
       </c>
-      <c r="P232" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>43556</v>
       </c>
@@ -11951,11 +11240,8 @@
       <c r="O233" s="8">
         <v>-5.1296383916635997E-2</v>
       </c>
-      <c r="P233" s="2">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>43586</v>
       </c>
@@ -11998,11 +11284,8 @@
       <c r="O234" s="8">
         <v>5.57194596484187E-2</v>
       </c>
-      <c r="P234" s="2">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>43617</v>
       </c>
@@ -12045,11 +11328,8 @@
       <c r="O235" s="8">
         <v>-1.70624874615601E-2</v>
       </c>
-      <c r="P235" s="2">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>43647</v>
       </c>
@@ -12092,11 +11372,8 @@
       <c r="O236" s="8">
         <v>-2.0703362979372E-2</v>
       </c>
-      <c r="P236" s="2">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>43678</v>
       </c>
@@ -12139,11 +11416,8 @@
       <c r="O237" s="8">
         <v>4.0124607332764101E-2</v>
       </c>
-      <c r="P237" s="2">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>43709</v>
       </c>
@@ -12186,11 +11460,8 @@
       <c r="O238" s="8">
         <v>3.4691141411061097E-2</v>
       </c>
-      <c r="P238" s="2">
-        <v>-2.6</v>
-      </c>
-    </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>43739</v>
       </c>
@@ -12233,11 +11504,8 @@
       <c r="O239" s="8">
         <v>2.8319514088868999E-2</v>
       </c>
-      <c r="P239" s="2">
-        <v>-4.7</v>
-      </c>
-    </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>43770</v>
       </c>
@@ -12280,11 +11548,8 @@
       <c r="O240" s="8">
         <v>9.5372459589704295E-4</v>
       </c>
-      <c r="P240" s="2">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>43800</v>
       </c>
@@ -12327,11 +11592,8 @@
       <c r="O241" s="8">
         <v>-2.03613643159084E-2</v>
       </c>
-      <c r="P241" s="2">
-        <v>-3.7</v>
-      </c>
-    </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>43831</v>
       </c>
@@ -12374,11 +11636,8 @@
       <c r="O242" s="8">
         <v>-8.7834336735301805E-2</v>
       </c>
-      <c r="P242" s="2">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>43862</v>
       </c>
@@ -12421,11 +11680,8 @@
       <c r="O243" s="8">
         <v>-0.17957870764244499</v>
       </c>
-      <c r="P243" s="2">
-        <v>-2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>43891</v>
       </c>
@@ -12468,11 +11724,8 @@
       <c r="O244" s="8">
         <v>8.9088877352494905E-2</v>
       </c>
-      <c r="P244" s="2">
-        <v>-8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>43922</v>
       </c>
@@ -12515,11 +11768,8 @@
       <c r="O245" s="8">
         <v>6.4633517047441899E-2</v>
       </c>
-      <c r="P245" s="2">
-        <v>-18.100000000000001</v>
-      </c>
-    </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>43952</v>
       </c>
@@ -12562,11 +11812,8 @@
       <c r="O246" s="8">
         <v>6.0616659617544102E-2</v>
       </c>
-      <c r="P246" s="2">
-        <v>-15.5</v>
-      </c>
-    </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>43983</v>
       </c>
@@ -12609,11 +11856,8 @@
       <c r="O247" s="8">
         <v>1.97420032540307E-4</v>
       </c>
-      <c r="P247" s="2">
-        <v>-10.1</v>
-      </c>
-    </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>44013</v>
       </c>
@@ -12656,11 +11900,8 @@
       <c r="O248" s="8">
         <v>5.0054078357490497E-2</v>
       </c>
-      <c r="P248" s="2">
-        <v>-9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>44044</v>
       </c>
@@ -12703,11 +11944,8 @@
       <c r="O249" s="8">
         <v>-1.43664356381485E-2</v>
       </c>
-      <c r="P249" s="2">
-        <v>-7.8</v>
-      </c>
-    </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>44075</v>
       </c>
@@ -12750,11 +11988,8 @@
       <c r="O250" s="8">
         <v>-9.9126163878370505E-2</v>
       </c>
-      <c r="P250" s="2">
-        <v>-7.2</v>
-      </c>
-    </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>44105</v>
       </c>
@@ -12797,11 +12032,8 @@
       <c r="O251" s="8">
         <v>0.13985280517704099</v>
       </c>
-      <c r="P251" s="2">
-        <v>-9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>44136</v>
       </c>
@@ -12844,11 +12076,8 @@
       <c r="O252" s="8">
         <v>3.1666552648804497E-2</v>
       </c>
-      <c r="P252" s="2">
-        <v>-10.9</v>
-      </c>
-    </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>44166</v>
       </c>
@@ -12891,11 +12120,8 @@
       <c r="O253" s="8">
         <v>-2.1061019894339901E-2</v>
       </c>
-      <c r="P253" s="2">
-        <v>-9.6999999999999993</v>
-      </c>
-    </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>44197</v>
       </c>
@@ -12938,11 +12164,8 @@
       <c r="O254" s="8">
         <v>2.5969925810608498E-2</v>
       </c>
-      <c r="P254" s="2">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>44228</v>
       </c>
@@ -12985,11 +12208,8 @@
       <c r="O255" s="8">
         <v>8.4931413271505093E-2</v>
       </c>
-      <c r="P255" s="2">
-        <v>-10.6</v>
-      </c>
-    </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>44256</v>
       </c>
@@ -13032,11 +12252,8 @@
       <c r="O256" s="8">
         <v>8.4640403455811305E-3</v>
       </c>
-      <c r="P256" s="2">
-        <v>-7.3</v>
-      </c>
-    </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>44287</v>
       </c>
@@ -13079,11 +12296,8 @@
       <c r="O257" s="8">
         <v>1.8668562777554201E-2</v>
       </c>
-      <c r="P257" s="2">
-        <v>-9.5</v>
-      </c>
-    </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>44317</v>
       </c>
@@ -13126,11 +12340,8 @@
       <c r="O258" s="8">
         <v>7.1019652901185299E-3</v>
       </c>
-      <c r="P258" s="2">
-        <v>-4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>44348</v>
       </c>
@@ -13173,11 +12384,8 @@
       <c r="O259" s="8">
         <v>8.5917461676032801E-4</v>
       </c>
-      <c r="P259" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>44378</v>
       </c>
@@ -13220,11 +12428,8 @@
       <c r="O260" s="8">
         <v>1.8528574508760401E-2</v>
       </c>
-      <c r="P260" s="2">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>44409</v>
       </c>
@@ -13267,11 +12472,8 @@
       <c r="O261" s="8">
         <v>-3.6948084477158402E-2</v>
       </c>
-      <c r="P261" s="2">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>44440</v>
       </c>
@@ -13314,11 +12516,8 @@
       <c r="O262" s="8">
         <v>2.7664870670250301E-2</v>
       </c>
-      <c r="P262" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>44470</v>
       </c>
@@ -13361,11 +12560,8 @@
       <c r="O263" s="8">
         <v>-3.8241794617819701E-2</v>
       </c>
-      <c r="P263" s="2">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>44501</v>
       </c>
@@ -13408,11 +12604,8 @@
       <c r="O264" s="8">
         <v>5.0663131173992702E-2</v>
       </c>
-      <c r="P264" s="2">
-        <v>-4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>44531</v>
       </c>
@@ -13455,11 +12648,8 @@
       <c r="O265" s="8">
         <v>-2.6386232778426302E-2</v>
       </c>
-      <c r="P265" s="2">
-        <v>-7.1</v>
-      </c>
-    </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>44562</v>
       </c>
@@ -13502,11 +12692,8 @@
       <c r="O266" s="8">
         <v>-6.7523522443023495E-2</v>
       </c>
-      <c r="P266" s="2">
-        <v>-5.3</v>
-      </c>
-    </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>44593</v>
       </c>
@@ -13549,11 +12736,8 @@
       <c r="O267" s="8">
         <v>-3.2047333526570299E-3</v>
       </c>
-      <c r="P267" s="2">
-        <v>-6.2</v>
-      </c>
-    </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>44621</v>
       </c>
@@ -13596,11 +12780,8 @@
       <c r="O268" s="8">
         <v>-2.22275647371468E-2</v>
       </c>
-      <c r="P268" s="2">
-        <v>-15.3</v>
-      </c>
-    </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>44652</v>
       </c>
@@ -13643,11 +12824,8 @@
       <c r="O269" s="8">
         <v>2.0394401058499802E-2</v>
       </c>
-      <c r="P269" s="2">
-        <v>-18.899999999999999</v>
-      </c>
-    </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>44682</v>
       </c>
@@ -13690,11 +12868,8 @@
       <c r="O270" s="8">
         <v>-0.118242463260449</v>
       </c>
-      <c r="P270" s="2">
-        <v>-18.3</v>
-      </c>
-    </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>44713</v>
       </c>
@@ -13737,11 +12912,8 @@
       <c r="O271" s="8">
         <v>5.3331130023282797E-2</v>
       </c>
-      <c r="P271" s="2">
-        <v>-19.899999999999999</v>
-      </c>
-    </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>44743</v>
       </c>
@@ -13784,11 +12956,8 @@
       <c r="O272" s="8">
         <v>-4.9334796182296997E-2</v>
       </c>
-      <c r="P272" s="2">
-        <v>-25.3</v>
-      </c>
-    </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>44774</v>
       </c>
@@ -13831,11 +13000,8 @@
       <c r="O273" s="8">
         <v>-5.7781139976897898E-2</v>
       </c>
-      <c r="P273" s="2">
-        <v>-24</v>
-      </c>
-    </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>44805</v>
       </c>
@@ -13878,11 +13044,8 @@
       <c r="O274" s="8">
         <v>8.9888239618305804E-2</v>
       </c>
-      <c r="P274" s="2">
-        <v>-29.4</v>
-      </c>
-    </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>44835</v>
       </c>
@@ -13925,11 +13088,8 @@
       <c r="O275" s="8">
         <v>8.2742838172361402E-2</v>
       </c>
-      <c r="P275" s="2">
-        <v>-28.4</v>
-      </c>
-    </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>44866</v>
       </c>
@@ -13972,11 +13132,8 @@
       <c r="O276" s="8">
         <v>-3.3438119878111301E-2</v>
       </c>
-      <c r="P276" s="2">
-        <v>-25.1</v>
-      </c>
-    </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>44896</v>
       </c>
@@ -14019,11 +13176,8 @@
       <c r="O277" s="8">
         <v>8.2980635179399798E-2</v>
       </c>
-      <c r="P277" s="2">
-        <v>-22.1</v>
-      </c>
-    </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>44927</v>
       </c>
@@ -14066,11 +13220,8 @@
       <c r="O278" s="8">
         <v>1.55361363662418E-2</v>
       </c>
-      <c r="P278" s="2">
-        <v>-19.2</v>
-      </c>
-    </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>44958</v>
       </c>
@@ -14113,11 +13264,8 @@
       <c r="O279" s="8">
         <v>1.7016631153158102E-2</v>
       </c>
-      <c r="P279" s="2">
-        <v>-15.8</v>
-      </c>
-    </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>44986</v>
       </c>
@@ -14160,11 +13308,8 @@
       <c r="O280" s="8">
         <v>1.8607743939233101E-2</v>
       </c>
-      <c r="P280" s="2">
-        <v>-17.100000000000001</v>
-      </c>
-    </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>45017</v>
       </c>
@@ -14207,11 +13352,8 @@
       <c r="O281" s="8">
         <v>-1.6359326694969301E-2</v>
       </c>
-      <c r="P281" s="2">
-        <v>-13.3</v>
-      </c>
-    </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>45047</v>
       </c>
@@ -14254,11 +13396,8 @@
       <c r="O282" s="8">
         <v>3.04237017694611E-2</v>
       </c>
-      <c r="P282" s="2">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>45078</v>
       </c>
@@ -14301,11 +13440,8 @@
       <c r="O283" s="8">
         <v>1.8342723779730001E-2</v>
       </c>
-      <c r="P283" s="2">
-        <v>-13.7</v>
-      </c>
-    </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>45108</v>
       </c>
@@ -14348,11 +13484,8 @@
       <c r="O284" s="8">
         <v>-3.0857012954521999E-2</v>
       </c>
-      <c r="P284" s="2">
-        <v>-13.5</v>
-      </c>
-    </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="285" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>45139</v>
       </c>
@@ -14395,11 +13528,8 @@
       <c r="O285" s="8">
         <v>-3.5780039258788997E-2</v>
       </c>
-      <c r="P285" s="2">
-        <v>-15.2</v>
-      </c>
-    </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="286" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>45170</v>
       </c>
@@ -14442,11 +13572,8 @@
       <c r="O286" s="8">
         <v>-3.8170131083722601E-2</v>
       </c>
-      <c r="P286" s="2">
-        <v>-15.9</v>
-      </c>
-    </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="287" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>45200</v>
       </c>
@@ -14489,11 +13616,8 @@
       <c r="O287" s="8">
         <v>9.0637663864162804E-2</v>
       </c>
-      <c r="P287" s="2">
-        <v>-15.5</v>
-      </c>
-    </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>45231</v>
       </c>
@@ -14536,11 +13660,8 @@
       <c r="O288" s="8">
         <v>3.2532962444236098E-2</v>
       </c>
-      <c r="P288" s="2">
-        <v>-16.5</v>
-      </c>
-    </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="289" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>45261</v>
       </c>
@@ -14583,11 +13704,8 @@
       <c r="O289" s="8">
         <v>9.0398672890046293E-3</v>
       </c>
-      <c r="P289" s="2">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="290" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>45292</v>
       </c>
@@ -14630,11 +13748,8 @@
       <c r="O290" s="8">
         <v>4.4795576943434098E-2</v>
       </c>
-      <c r="P290" s="2">
-        <v>-17.3</v>
-      </c>
-    </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="291" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>45323</v>
       </c>
@@ -14677,11 +13792,8 @@
       <c r="O291" s="8">
         <v>4.5033070925896403E-2</v>
       </c>
-      <c r="P291" s="2">
-        <v>-14.3</v>
-      </c>
-    </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="292" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>45352</v>
       </c>
@@ -14724,11 +13836,8 @@
       <c r="O292" s="8">
         <v>-3.0768414243720298E-2</v>
       </c>
-      <c r="P292" s="2">
-        <v>-13.4</v>
-      </c>
-    </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="293" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>45383</v>
       </c>
@@ -14771,11 +13880,8 @@
       <c r="O293" s="8">
         <v>3.1063042818486201E-2</v>
       </c>
-      <c r="P293" s="2">
-        <v>-10.1</v>
-      </c>
-    </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="294" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>45413</v>
       </c>
@@ -14818,11 +13924,8 @@
       <c r="O294" s="8">
         <v>-1.42918860376433E-2</v>
       </c>
-      <c r="P294" s="2">
-        <v>-9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="295" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>45444</v>
       </c>
@@ -14865,11 +13968,8 @@
       <c r="O295" s="8">
         <v>1.4870752550031299E-2</v>
       </c>
-      <c r="P295" s="2">
-        <v>-9.9</v>
-      </c>
-    </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="296" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>45474</v>
       </c>
@@ -14912,11 +14012,8 @@
       <c r="O296" s="8">
         <v>2.12897770064568E-2</v>
       </c>
-      <c r="P296" s="2">
-        <v>-7.7</v>
-      </c>
-    </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="297" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>45505</v>
       </c>
@@ -14959,11 +14056,8 @@
       <c r="O297" s="8">
         <v>2.1867967557486899E-2</v>
       </c>
-      <c r="P297" s="2">
-        <v>-9.9</v>
-      </c>
-    </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="298" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>45536</v>
       </c>
@@ -15006,11 +14100,8 @@
       <c r="O298" s="8">
         <v>-1.28842782964522E-2</v>
       </c>
-      <c r="P298" s="2">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="299" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>45566</v>
       </c>
@@ -15053,11 +14144,8 @@
       <c r="O299" s="8">
         <v>2.83664287347438E-2</v>
       </c>
-      <c r="P299" s="2">
-        <v>-9</v>
-      </c>
-    </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="300" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>45597</v>
       </c>
@@ -15100,11 +14188,8 @@
       <c r="O300" s="8">
         <v>1.43008476777062E-2</v>
       </c>
-      <c r="P300" s="2">
-        <v>-11.4</v>
-      </c>
-    </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="301" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>45627</v>
       </c>
@@ -15147,11 +14232,8 @@
       <c r="O301" s="8">
         <v>8.76092112293545E-2</v>
       </c>
-      <c r="P301" s="2">
-        <v>-10.5</v>
-      </c>
-    </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="302" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>45658</v>
       </c>
@@ -15194,11 +14276,8 @@
       <c r="O302" s="8">
         <v>3.7010299324510498E-2</v>
       </c>
-      <c r="P302" s="2">
-        <v>-11.9</v>
-      </c>
-    </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="303" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>45689</v>
       </c>
@@ -15241,11 +14320,8 @@
       <c r="O303" s="8">
         <v>-1.7352113686762E-2</v>
       </c>
-      <c r="P303" s="2">
-        <v>-11.4</v>
-      </c>
-    </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="304" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>45717</v>
       </c>
@@ -15288,11 +14364,8 @@
       <c r="O304" s="8">
         <v>1.4934747787439299E-2</v>
       </c>
-      <c r="P304" s="2">
-        <v>-10.1</v>
-      </c>
-    </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="305" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>45748</v>
       </c>
@@ -15335,11 +14408,8 @@
       <c r="O305" s="8">
         <v>6.4567745552686504E-2</v>
       </c>
-      <c r="P305" s="2">
-        <v>-10.7</v>
-      </c>
-    </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="306" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>45778</v>
       </c>
@@ -15382,11 +14452,8 @@
       <c r="O306" s="8">
         <v>-3.6684003381495201E-3</v>
       </c>
-      <c r="P306" s="2">
-        <v>-8.6999999999999993</v>
-      </c>
-    </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="307" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>45809</v>
       </c>
@@ -15429,11 +14496,8 @@
       <c r="O307" s="8">
         <v>6.4976181897140597E-3</v>
       </c>
-      <c r="P307" s="2">
-        <v>-8.8000000000000007</v>
-      </c>
-    </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="308" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>45839</v>
       </c>
@@ -15476,11 +14540,8 @@
       <c r="O308" s="8">
         <v>-6.80709971585891E-3</v>
       </c>
-      <c r="P308" s="2">
-        <v>-8.4</v>
-      </c>
-    </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="309" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>45870</v>
       </c>
@@ -15523,11 +14584,8 @@
       <c r="O309" s="8">
         <v>-8.9949423721336096E-4</v>
       </c>
-      <c r="P309" s="2">
-        <v>-10.6</v>
-      </c>
-    </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="310" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>45901</v>
       </c>
@@ -15570,11 +14628,8 @@
       <c r="O310" s="8">
         <v>3.2433834859766399E-3</v>
       </c>
-      <c r="P310" s="2">
-        <v>-9.3000000000000007</v>
-      </c>
-    </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="311" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>45931</v>
       </c>
@@ -15617,11 +14672,8 @@
       <c r="O311" s="8">
         <v>-5.0847056024565501E-3</v>
       </c>
-      <c r="P311" s="2">
-        <v>-10.9</v>
-      </c>
-    </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="312" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A312" s="1">
         <v>45962</v>
       </c>
@@ -15664,11 +14716,8 @@
       <c r="O312" s="8">
         <v>2.7051472580767601E-2</v>
       </c>
-      <c r="P312" s="2">
-        <v>-11.5</v>
-      </c>
-    </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="313" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A313" s="1">
         <v>45992</v>
       </c>
@@ -15710,9 +14759,6 @@
       </c>
       <c r="O313" s="8">
         <v>2.5679690612724598E-2</v>
-      </c>
-      <c r="P313" s="2">
-        <v>-12</v>
       </c>
     </row>
   </sheetData>
@@ -15723,8 +14769,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E2AD087-7DFA-7B41-801D-0DC7D7892A01}">
-  <dimension ref="A1:S313"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Q313"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -15735,39 +14781,39 @@
     <col min="17" max="17" width="27.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>18</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>19</v>
       </c>
       <c r="L1" s="11" t="s">
         <v>3</v>
@@ -15779,16 +14825,16 @@
         <v>2</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P1" s="11" t="s">
         <v>7</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>36526</v>
       </c>
@@ -15834,12 +14880,8 @@
       <c r="Q2" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S2" t="str">
-        <f>IF(MONTH($A2) = 1, YEAR($A2)&amp;"-Q"&amp;MONTH($A2), IF(MONTH($A2) = 4, YEAR($A2)&amp;"-Q2", IF(MONTH($A2) = 7, YEAR($A2)&amp;"-Q3", IF(MONTH($A2) = 10, YEAR($A2)&amp;"-Q4",""))))</f>
-        <v>2000-Q1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>36557</v>
       </c>
@@ -15885,12 +14927,8 @@
       <c r="Q3" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S3" t="str">
-        <f t="shared" ref="S3:S66" si="0">IF(MONTH($A3) = 1, YEAR($A3)&amp;"-Q"&amp;MONTH($A3), IF(MONTH($A3) = 4, YEAR($A3)&amp;"-Q2", IF(MONTH($A3) = 7, YEAR($A3)&amp;"-Q3", IF(MONTH($A3) = 10, YEAR($A3)&amp;"-Q4",""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>36586</v>
       </c>
@@ -15936,12 +14974,8 @@
       <c r="Q4" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>36617</v>
       </c>
@@ -15987,12 +15021,8 @@
       <c r="Q5" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S5" t="str">
-        <f t="shared" si="0"/>
-        <v>2000-Q2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>36647</v>
       </c>
@@ -16038,12 +15068,8 @@
       <c r="Q6" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S6" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>36678</v>
       </c>
@@ -16089,12 +15115,8 @@
       <c r="Q7" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S7" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>36708</v>
       </c>
@@ -16140,12 +15162,8 @@
       <c r="Q8" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S8" t="str">
-        <f t="shared" si="0"/>
-        <v>2000-Q3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>36739</v>
       </c>
@@ -16191,12 +15209,8 @@
       <c r="Q9" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>36770</v>
       </c>
@@ -16240,14 +15254,10 @@
         <v>64.179659999999998</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>36800</v>
       </c>
@@ -16293,12 +15303,8 @@
       <c r="Q11" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S11" t="str">
-        <f t="shared" si="0"/>
-        <v>2000-Q4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>36831</v>
       </c>
@@ -16344,12 +15350,8 @@
       <c r="Q12" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>36861</v>
       </c>
@@ -16395,12 +15397,8 @@
       <c r="Q13" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>36892</v>
       </c>
@@ -16446,12 +15444,8 @@
       <c r="Q14" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S14" t="str">
-        <f t="shared" si="0"/>
-        <v>2001-Q1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>36923</v>
       </c>
@@ -16497,12 +15491,8 @@
       <c r="Q15" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>36951</v>
       </c>
@@ -16548,12 +15538,8 @@
       <c r="Q16" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>36982</v>
       </c>
@@ -16599,12 +15585,8 @@
       <c r="Q17" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S17" t="str">
-        <f t="shared" si="0"/>
-        <v>2001-Q2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>37012</v>
       </c>
@@ -16650,12 +15632,8 @@
       <c r="Q18" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>37043</v>
       </c>
@@ -16701,12 +15679,8 @@
       <c r="Q19" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>37073</v>
       </c>
@@ -16752,12 +15726,8 @@
       <c r="Q20" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S20" t="str">
-        <f t="shared" si="0"/>
-        <v>2001-Q3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>37104</v>
       </c>
@@ -16803,12 +15773,8 @@
       <c r="Q21" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>37135</v>
       </c>
@@ -16854,12 +15820,8 @@
       <c r="Q22" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S22" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>37165</v>
       </c>
@@ -16905,12 +15867,8 @@
       <c r="Q23" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S23" t="str">
-        <f t="shared" si="0"/>
-        <v>2001-Q4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>37196</v>
       </c>
@@ -16956,12 +15914,8 @@
       <c r="Q24" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S24" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>37226</v>
       </c>
@@ -17007,12 +15961,8 @@
       <c r="Q25" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S25" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>37257</v>
       </c>
@@ -17058,12 +16008,8 @@
       <c r="Q26" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S26" t="str">
-        <f t="shared" si="0"/>
-        <v>2002-Q1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>37288</v>
       </c>
@@ -17109,12 +16055,8 @@
       <c r="Q27" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>37316</v>
       </c>
@@ -17160,12 +16102,8 @@
       <c r="Q28" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S28" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>37347</v>
       </c>
@@ -17211,12 +16149,8 @@
       <c r="Q29" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S29" t="str">
-        <f t="shared" si="0"/>
-        <v>2002-Q2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>37377</v>
       </c>
@@ -17262,12 +16196,8 @@
       <c r="Q30" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S30" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>37408</v>
       </c>
@@ -17313,12 +16243,8 @@
       <c r="Q31" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S31" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>37438</v>
       </c>
@@ -17364,12 +16290,8 @@
       <c r="Q32" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S32" t="str">
-        <f t="shared" si="0"/>
-        <v>2002-Q3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>37469</v>
       </c>
@@ -17415,12 +16337,8 @@
       <c r="Q33" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S33" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>37500</v>
       </c>
@@ -17466,12 +16384,8 @@
       <c r="Q34" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>37530</v>
       </c>
@@ -17517,12 +16431,8 @@
       <c r="Q35" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S35" t="str">
-        <f t="shared" si="0"/>
-        <v>2002-Q4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>37561</v>
       </c>
@@ -17568,12 +16478,8 @@
       <c r="Q36" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>37591</v>
       </c>
@@ -17619,12 +16525,8 @@
       <c r="Q37" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S37" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>37622</v>
       </c>
@@ -17670,12 +16572,8 @@
       <c r="Q38" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S38" t="str">
-        <f t="shared" si="0"/>
-        <v>2003-Q1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>37653</v>
       </c>
@@ -17721,12 +16619,8 @@
       <c r="Q39" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S39" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>37681</v>
       </c>
@@ -17772,12 +16666,8 @@
       <c r="Q40" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S40" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>37712</v>
       </c>
@@ -17823,12 +16713,8 @@
       <c r="Q41" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S41" t="str">
-        <f t="shared" si="0"/>
-        <v>2003-Q2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>37742</v>
       </c>
@@ -17874,12 +16760,8 @@
       <c r="Q42" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S42" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>37773</v>
       </c>
@@ -17925,12 +16807,8 @@
       <c r="Q43" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S43" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>37803</v>
       </c>
@@ -17976,12 +16854,8 @@
       <c r="Q44" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S44" t="str">
-        <f t="shared" si="0"/>
-        <v>2003-Q3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>37834</v>
       </c>
@@ -18027,12 +16901,8 @@
       <c r="Q45" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S45" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>37865</v>
       </c>
@@ -18078,12 +16948,8 @@
       <c r="Q46" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S46" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>37895</v>
       </c>
@@ -18129,12 +16995,8 @@
       <c r="Q47" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S47" t="str">
-        <f t="shared" si="0"/>
-        <v>2003-Q4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>37926</v>
       </c>
@@ -18180,12 +17042,8 @@
       <c r="Q48" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S48" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>37956</v>
       </c>
@@ -18231,12 +17089,8 @@
       <c r="Q49" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S49" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>37987</v>
       </c>
@@ -18282,12 +17136,8 @@
       <c r="Q50" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S50" t="str">
-        <f t="shared" si="0"/>
-        <v>2004-Q1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>38018</v>
       </c>
@@ -18333,12 +17183,8 @@
       <c r="Q51" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S51" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>38047</v>
       </c>
@@ -18384,12 +17230,8 @@
       <c r="Q52" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S52" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>38078</v>
       </c>
@@ -18435,12 +17277,8 @@
       <c r="Q53" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S53" t="str">
-        <f t="shared" si="0"/>
-        <v>2004-Q2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>38108</v>
       </c>
@@ -18486,12 +17324,8 @@
       <c r="Q54" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S54" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>38139</v>
       </c>
@@ -18537,12 +17371,8 @@
       <c r="Q55" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S55" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>38169</v>
       </c>
@@ -18588,12 +17418,8 @@
       <c r="Q56" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S56" t="str">
-        <f t="shared" si="0"/>
-        <v>2004-Q3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>38200</v>
       </c>
@@ -18639,12 +17465,8 @@
       <c r="Q57" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S57" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>38231</v>
       </c>
@@ -18690,12 +17512,8 @@
       <c r="Q58" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S58" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>38261</v>
       </c>
@@ -18741,12 +17559,8 @@
       <c r="Q59" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S59" t="str">
-        <f t="shared" si="0"/>
-        <v>2004-Q4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>38292</v>
       </c>
@@ -18792,12 +17606,8 @@
       <c r="Q60" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S60" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>38322</v>
       </c>
@@ -18843,12 +17653,8 @@
       <c r="Q61" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S61" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>38353</v>
       </c>
@@ -18894,12 +17700,8 @@
       <c r="Q62" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S62" t="str">
-        <f t="shared" si="0"/>
-        <v>2005-Q1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>38384</v>
       </c>
@@ -18945,12 +17747,8 @@
       <c r="Q63" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S63" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>38412</v>
       </c>
@@ -18996,12 +17794,8 @@
       <c r="Q64" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S64" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>38443</v>
       </c>
@@ -19047,12 +17841,8 @@
       <c r="Q65" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S65" t="str">
-        <f t="shared" si="0"/>
-        <v>2005-Q2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>38473</v>
       </c>
@@ -19098,12 +17888,8 @@
       <c r="Q66" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S66" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>38504</v>
       </c>
@@ -19149,12 +17935,8 @@
       <c r="Q67" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S67" t="str">
-        <f t="shared" ref="S67:S130" si="1">IF(MONTH($A67) = 1, YEAR($A67)&amp;"-Q"&amp;MONTH($A67), IF(MONTH($A67) = 4, YEAR($A67)&amp;"-Q2", IF(MONTH($A67) = 7, YEAR($A67)&amp;"-Q3", IF(MONTH($A67) = 10, YEAR($A67)&amp;"-Q4",""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>38534</v>
       </c>
@@ -19200,12 +17982,8 @@
       <c r="Q68" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S68" t="str">
-        <f t="shared" si="1"/>
-        <v>2005-Q3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>38565</v>
       </c>
@@ -19251,12 +18029,8 @@
       <c r="Q69" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S69" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>38596</v>
       </c>
@@ -19302,12 +18076,8 @@
       <c r="Q70" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S70" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>38626</v>
       </c>
@@ -19353,12 +18123,8 @@
       <c r="Q71" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S71" t="str">
-        <f t="shared" si="1"/>
-        <v>2005-Q4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>38657</v>
       </c>
@@ -19402,14 +18168,10 @@
         <v>78.822850000000003</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S72" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>38687</v>
       </c>
@@ -19455,12 +18217,8 @@
       <c r="Q73" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S73" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>38718</v>
       </c>
@@ -19506,12 +18264,8 @@
       <c r="Q74" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S74" t="str">
-        <f t="shared" si="1"/>
-        <v>2006-Q1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>38749</v>
       </c>
@@ -19557,12 +18311,8 @@
       <c r="Q75" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S75" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>38777</v>
       </c>
@@ -19608,12 +18358,8 @@
       <c r="Q76" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S76" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>38808</v>
       </c>
@@ -19659,12 +18405,8 @@
       <c r="Q77" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S77" t="str">
-        <f t="shared" si="1"/>
-        <v>2006-Q2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>38838</v>
       </c>
@@ -19710,12 +18452,8 @@
       <c r="Q78" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S78" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>38869</v>
       </c>
@@ -19761,12 +18499,8 @@
       <c r="Q79" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S79" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>38899</v>
       </c>
@@ -19812,12 +18546,8 @@
       <c r="Q80" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S80" t="str">
-        <f t="shared" si="1"/>
-        <v>2006-Q3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>38930</v>
       </c>
@@ -19863,12 +18593,8 @@
       <c r="Q81" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S81" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>38961</v>
       </c>
@@ -19914,12 +18640,8 @@
       <c r="Q82" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S82" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>38991</v>
       </c>
@@ -19965,12 +18687,8 @@
       <c r="Q83" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S83" t="str">
-        <f t="shared" si="1"/>
-        <v>2006-Q4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>39022</v>
       </c>
@@ -20016,12 +18734,8 @@
       <c r="Q84" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S84" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>39052</v>
       </c>
@@ -20067,12 +18781,8 @@
       <c r="Q85" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S85" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>39083</v>
       </c>
@@ -20118,12 +18828,8 @@
       <c r="Q86" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S86" t="str">
-        <f t="shared" si="1"/>
-        <v>2007-Q1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>39114</v>
       </c>
@@ -20169,12 +18875,8 @@
       <c r="Q87" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S87" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>39142</v>
       </c>
@@ -20220,12 +18922,8 @@
       <c r="Q88" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S88" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>39173</v>
       </c>
@@ -20271,12 +18969,8 @@
       <c r="Q89" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S89" t="str">
-        <f t="shared" si="1"/>
-        <v>2007-Q2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>39203</v>
       </c>
@@ -20322,12 +19016,8 @@
       <c r="Q90" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S90" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>39234</v>
       </c>
@@ -20373,12 +19063,8 @@
       <c r="Q91" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S91" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>39264</v>
       </c>
@@ -20424,12 +19110,8 @@
       <c r="Q92" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S92" t="str">
-        <f t="shared" si="1"/>
-        <v>2007-Q3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>39295</v>
       </c>
@@ -20475,12 +19157,8 @@
       <c r="Q93" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S93" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>39326</v>
       </c>
@@ -20526,12 +19204,8 @@
       <c r="Q94" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S94" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>39356</v>
       </c>
@@ -20577,12 +19251,8 @@
       <c r="Q95" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S95" t="str">
-        <f t="shared" si="1"/>
-        <v>2007-Q4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>39387</v>
       </c>
@@ -20628,12 +19298,8 @@
       <c r="Q96" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S96" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>39417</v>
       </c>
@@ -20679,12 +19345,8 @@
       <c r="Q97" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S97" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>39448</v>
       </c>
@@ -20730,12 +19392,8 @@
       <c r="Q98" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S98" t="str">
-        <f t="shared" si="1"/>
-        <v>2008-Q1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>39479</v>
       </c>
@@ -20781,12 +19439,8 @@
       <c r="Q99" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S99" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>39508</v>
       </c>
@@ -20832,12 +19486,8 @@
       <c r="Q100" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S100" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>39539</v>
       </c>
@@ -20883,12 +19533,8 @@
       <c r="Q101" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S101" t="str">
-        <f t="shared" si="1"/>
-        <v>2008-Q2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>39569</v>
       </c>
@@ -20934,12 +19580,8 @@
       <c r="Q102" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S102" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>39600</v>
       </c>
@@ -20985,12 +19627,8 @@
       <c r="Q103" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S103" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>39630</v>
       </c>
@@ -21036,12 +19674,8 @@
       <c r="Q104" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S104" t="str">
-        <f t="shared" si="1"/>
-        <v>2008-Q3</v>
-      </c>
-    </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>39661</v>
       </c>
@@ -21087,12 +19721,8 @@
       <c r="Q105" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S105" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>39692</v>
       </c>
@@ -21138,12 +19768,8 @@
       <c r="Q106" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S106" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>39722</v>
       </c>
@@ -21189,12 +19815,8 @@
       <c r="Q107" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S107" t="str">
-        <f t="shared" si="1"/>
-        <v>2008-Q4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>39753</v>
       </c>
@@ -21240,12 +19862,8 @@
       <c r="Q108" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S108" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>39783</v>
       </c>
@@ -21291,12 +19909,8 @@
       <c r="Q109" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S109" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>39814</v>
       </c>
@@ -21342,12 +19956,8 @@
       <c r="Q110" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S110" t="str">
-        <f t="shared" si="1"/>
-        <v>2009-Q1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>39845</v>
       </c>
@@ -21393,12 +20003,8 @@
       <c r="Q111" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S111" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>39873</v>
       </c>
@@ -21444,12 +20050,8 @@
       <c r="Q112" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S112" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>39904</v>
       </c>
@@ -21495,12 +20097,8 @@
       <c r="Q113" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S113" t="str">
-        <f t="shared" si="1"/>
-        <v>2009-Q2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>39934</v>
       </c>
@@ -21546,12 +20144,8 @@
       <c r="Q114" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S114" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>39965</v>
       </c>
@@ -21597,12 +20191,8 @@
       <c r="Q115" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S115" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>39995</v>
       </c>
@@ -21648,12 +20238,8 @@
       <c r="Q116" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S116" t="str">
-        <f t="shared" si="1"/>
-        <v>2009-Q3</v>
-      </c>
-    </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>40026</v>
       </c>
@@ -21699,12 +20285,8 @@
       <c r="Q117" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S117" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>40057</v>
       </c>
@@ -21750,12 +20332,8 @@
       <c r="Q118" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S118" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>40087</v>
       </c>
@@ -21801,12 +20379,8 @@
       <c r="Q119" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S119" t="str">
-        <f t="shared" si="1"/>
-        <v>2009-Q4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>40118</v>
       </c>
@@ -21852,12 +20426,8 @@
       <c r="Q120" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S120" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>40148</v>
       </c>
@@ -21903,12 +20473,8 @@
       <c r="Q121" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S121" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>40179</v>
       </c>
@@ -21954,12 +20520,8 @@
       <c r="Q122" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S122" t="str">
-        <f t="shared" si="1"/>
-        <v>2010-Q1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>40210</v>
       </c>
@@ -22005,12 +20567,8 @@
       <c r="Q123" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S123" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>40238</v>
       </c>
@@ -22056,12 +20614,8 @@
       <c r="Q124" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S124" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>40269</v>
       </c>
@@ -22107,12 +20661,8 @@
       <c r="Q125" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S125" t="str">
-        <f t="shared" si="1"/>
-        <v>2010-Q2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>40299</v>
       </c>
@@ -22158,12 +20708,8 @@
       <c r="Q126" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S126" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>40330</v>
       </c>
@@ -22209,12 +20755,8 @@
       <c r="Q127" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S127" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>40360</v>
       </c>
@@ -22260,12 +20802,8 @@
       <c r="Q128" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S128" t="str">
-        <f t="shared" si="1"/>
-        <v>2010-Q3</v>
-      </c>
-    </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>40391</v>
       </c>
@@ -22311,12 +20849,8 @@
       <c r="Q129" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S129" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>40422</v>
       </c>
@@ -22362,12 +20896,8 @@
       <c r="Q130" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S130" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>40452</v>
       </c>
@@ -22413,12 +20943,8 @@
       <c r="Q131" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S131" t="str">
-        <f t="shared" ref="S131:S194" si="2">IF(MONTH($A131) = 1, YEAR($A131)&amp;"-Q"&amp;MONTH($A131), IF(MONTH($A131) = 4, YEAR($A131)&amp;"-Q2", IF(MONTH($A131) = 7, YEAR($A131)&amp;"-Q3", IF(MONTH($A131) = 10, YEAR($A131)&amp;"-Q4",""))))</f>
-        <v>2010-Q4</v>
-      </c>
-    </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>40483</v>
       </c>
@@ -22464,12 +20990,8 @@
       <c r="Q132" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S132" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>40513</v>
       </c>
@@ -22515,12 +21037,8 @@
       <c r="Q133" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S133" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>40544</v>
       </c>
@@ -22566,12 +21084,8 @@
       <c r="Q134" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S134" t="str">
-        <f t="shared" si="2"/>
-        <v>2011-Q1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>40575</v>
       </c>
@@ -22617,12 +21131,8 @@
       <c r="Q135" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S135" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>40603</v>
       </c>
@@ -22668,12 +21178,8 @@
       <c r="Q136" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S136" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>40634</v>
       </c>
@@ -22719,12 +21225,8 @@
       <c r="Q137" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S137" t="str">
-        <f t="shared" si="2"/>
-        <v>2011-Q2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>40664</v>
       </c>
@@ -22770,12 +21272,8 @@
       <c r="Q138" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S138" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>40695</v>
       </c>
@@ -22821,12 +21319,8 @@
       <c r="Q139" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S139" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>40725</v>
       </c>
@@ -22872,12 +21366,8 @@
       <c r="Q140" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S140" t="str">
-        <f t="shared" si="2"/>
-        <v>2011-Q3</v>
-      </c>
-    </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>40756</v>
       </c>
@@ -22923,12 +21413,8 @@
       <c r="Q141" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S141" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>40787</v>
       </c>
@@ -22972,14 +21458,10 @@
         <v>104.0934</v>
       </c>
       <c r="Q142" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S142" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>40817</v>
       </c>
@@ -23025,12 +21507,8 @@
       <c r="Q143" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S143" t="str">
-        <f t="shared" si="2"/>
-        <v>2011-Q4</v>
-      </c>
-    </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>40848</v>
       </c>
@@ -23074,14 +21552,10 @@
         <v>105.0398</v>
       </c>
       <c r="Q144" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S144" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>40878</v>
       </c>
@@ -23125,14 +21599,10 @@
         <v>104.1986</v>
       </c>
       <c r="Q145" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="S145" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>40909</v>
       </c>
@@ -23176,14 +21646,10 @@
         <v>106.16379999999999</v>
       </c>
       <c r="Q146" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S146" t="str">
-        <f t="shared" si="2"/>
-        <v>2012-Q1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>40940</v>
       </c>
@@ -23227,14 +21693,10 @@
         <v>107.7054</v>
       </c>
       <c r="Q147" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S147" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>40969</v>
       </c>
@@ -23280,12 +21742,8 @@
       <c r="Q148" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>41000</v>
       </c>
@@ -23331,12 +21789,8 @@
       <c r="Q149" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S149" t="str">
-        <f t="shared" si="2"/>
-        <v>2012-Q2</v>
-      </c>
-    </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>41030</v>
       </c>
@@ -23380,14 +21834,10 @@
         <v>108.2723</v>
       </c>
       <c r="Q150" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S150" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>41061</v>
       </c>
@@ -23433,12 +21883,8 @@
       <c r="Q151" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S151" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>41091</v>
       </c>
@@ -23482,14 +21928,10 @@
         <v>107.8237</v>
       </c>
       <c r="Q152" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S152" t="str">
-        <f t="shared" si="2"/>
-        <v>2012-Q3</v>
-      </c>
-    </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>41122</v>
       </c>
@@ -23533,14 +21975,10 @@
         <v>110.23739999999999</v>
       </c>
       <c r="Q153" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S153" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>41153</v>
       </c>
@@ -23586,12 +22024,8 @@
       <c r="Q154" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S154" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>41183</v>
       </c>
@@ -23637,12 +22071,8 @@
       <c r="Q155" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S155" t="str">
-        <f t="shared" si="2"/>
-        <v>2012-Q4</v>
-      </c>
-    </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>41214</v>
       </c>
@@ -23688,12 +22118,8 @@
       <c r="Q156" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S156" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>41244</v>
       </c>
@@ -23739,12 +22165,8 @@
       <c r="Q157" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S157" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>41275</v>
       </c>
@@ -23790,12 +22212,8 @@
       <c r="Q158" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S158" t="str">
-        <f t="shared" si="2"/>
-        <v>2013-Q1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>41306</v>
       </c>
@@ -23821,7 +22239,7 @@
         <v>#N/A</v>
       </c>
       <c r="I159" s="4">
-        <v>0.32761001586914063</v>
+        <v>0.32761001586914062</v>
       </c>
       <c r="L159">
         <v>100</v>
@@ -23839,14 +22257,10 @@
         <v>111.57810000000001</v>
       </c>
       <c r="Q159" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S159" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>41334</v>
       </c>
@@ -23892,12 +22306,8 @@
       <c r="Q160" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S160" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>41365</v>
       </c>
@@ -23943,12 +22353,8 @@
       <c r="Q161" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S161" t="str">
-        <f t="shared" si="2"/>
-        <v>2013-Q2</v>
-      </c>
-    </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>41395</v>
       </c>
@@ -23992,14 +22398,10 @@
         <v>109.8737</v>
       </c>
       <c r="Q162" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S162" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>41426</v>
       </c>
@@ -24043,14 +22445,10 @@
         <v>109.8146</v>
       </c>
       <c r="Q163" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S163" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>41456</v>
       </c>
@@ -24094,14 +22492,10 @@
         <v>111.008</v>
       </c>
       <c r="Q164" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S164" t="str">
-        <f t="shared" si="2"/>
-        <v>2013-Q3</v>
-      </c>
-    </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>41487</v>
       </c>
@@ -24147,12 +22541,8 @@
       <c r="Q165" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S165" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>41518</v>
       </c>
@@ -24196,14 +22586,10 @@
         <v>111.2007</v>
       </c>
       <c r="Q166" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S166" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>41548</v>
       </c>
@@ -24247,14 +22633,10 @@
         <v>109.67959999999999</v>
       </c>
       <c r="Q167" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S167" t="str">
-        <f t="shared" si="2"/>
-        <v>2013-Q4</v>
-      </c>
-    </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>41579</v>
       </c>
@@ -24298,14 +22680,10 @@
         <v>108.6388</v>
       </c>
       <c r="Q168" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S168" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>41609</v>
       </c>
@@ -24351,12 +22729,8 @@
       <c r="Q169" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S169" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>41640</v>
       </c>
@@ -24400,14 +22774,10 @@
         <v>108.28959999999999</v>
       </c>
       <c r="Q170" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S170" t="str">
-        <f t="shared" si="2"/>
-        <v>2014-Q1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>41671</v>
       </c>
@@ -24451,14 +22821,10 @@
         <v>108.5836</v>
       </c>
       <c r="Q171" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S171" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>41699</v>
       </c>
@@ -24502,14 +22868,10 @@
         <v>108.1872</v>
       </c>
       <c r="Q172" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S172" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>41730</v>
       </c>
@@ -24553,14 +22915,10 @@
         <v>108.9447</v>
       </c>
       <c r="Q173" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S173" t="str">
-        <f t="shared" si="2"/>
-        <v>2014-Q2</v>
-      </c>
-    </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>41760</v>
       </c>
@@ -24604,14 +22962,10 @@
         <v>108.9581</v>
       </c>
       <c r="Q174" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S174" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>41791</v>
       </c>
@@ -24655,14 +23009,10 @@
         <v>109.4795</v>
       </c>
       <c r="Q175" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S175" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>41821</v>
       </c>
@@ -24706,14 +23056,10 @@
         <v>109.2924</v>
       </c>
       <c r="Q176" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S176" t="str">
-        <f t="shared" si="2"/>
-        <v>2014-Q3</v>
-      </c>
-    </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>41852</v>
       </c>
@@ -24757,14 +23103,10 @@
         <v>108.6729</v>
       </c>
       <c r="Q177" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S177" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>41883</v>
       </c>
@@ -24808,14 +23150,10 @@
         <v>108.8155</v>
       </c>
       <c r="Q178" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S178" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>41913</v>
       </c>
@@ -24859,14 +23197,10 @@
         <v>107.22969999999999</v>
       </c>
       <c r="Q179" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S179" t="str">
-        <f t="shared" si="2"/>
-        <v>2014-Q4</v>
-      </c>
-    </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>41944</v>
       </c>
@@ -24912,12 +23246,8 @@
       <c r="Q180" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S180" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>41974</v>
       </c>
@@ -24963,12 +23293,8 @@
       <c r="Q181" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S181" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>42005</v>
       </c>
@@ -25014,12 +23340,8 @@
       <c r="Q182" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S182" t="str">
-        <f t="shared" si="2"/>
-        <v>2015-Q1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>42036</v>
       </c>
@@ -25065,12 +23387,8 @@
       <c r="Q183" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S183" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="184" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>42064</v>
       </c>
@@ -25116,12 +23434,8 @@
       <c r="Q184" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S184" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="185" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>42095</v>
       </c>
@@ -25167,12 +23481,8 @@
       <c r="Q185" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S185" t="str">
-        <f t="shared" si="2"/>
-        <v>2015-Q2</v>
-      </c>
-    </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>42125</v>
       </c>
@@ -25218,12 +23528,8 @@
       <c r="Q186" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S186" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>42156</v>
       </c>
@@ -25269,12 +23575,8 @@
       <c r="Q187" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S187" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="188" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>42186</v>
       </c>
@@ -25320,12 +23622,8 @@
       <c r="Q188" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S188" t="str">
-        <f t="shared" si="2"/>
-        <v>2015-Q3</v>
-      </c>
-    </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="189" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>42217</v>
       </c>
@@ -25371,12 +23669,8 @@
       <c r="Q189" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S189" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="190" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>42248</v>
       </c>
@@ -25422,12 +23716,8 @@
       <c r="Q190" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S190" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="191" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>42278</v>
       </c>
@@ -25473,12 +23763,8 @@
       <c r="Q191" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S191" t="str">
-        <f t="shared" si="2"/>
-        <v>2015-Q4</v>
-      </c>
-    </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="192" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>42309</v>
       </c>
@@ -25524,12 +23810,8 @@
       <c r="Q192" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S192" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="193" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>42339</v>
       </c>
@@ -25575,12 +23857,8 @@
       <c r="Q193" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S193" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="194" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>42370</v>
       </c>
@@ -25624,14 +23902,10 @@
         <v>93.082849999999993</v>
       </c>
       <c r="Q194" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S194" t="str">
-        <f t="shared" si="2"/>
-        <v>2016-Q1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>42401</v>
       </c>
@@ -25677,12 +23951,8 @@
       <c r="Q195" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S195" t="str">
-        <f t="shared" ref="S195:S258" si="3">IF(MONTH($A195) = 1, YEAR($A195)&amp;"-Q"&amp;MONTH($A195), IF(MONTH($A195) = 4, YEAR($A195)&amp;"-Q2", IF(MONTH($A195) = 7, YEAR($A195)&amp;"-Q3", IF(MONTH($A195) = 10, YEAR($A195)&amp;"-Q4",""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="196" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>42430</v>
       </c>
@@ -25728,12 +23998,8 @@
       <c r="Q196" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S196" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="197" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>42461</v>
       </c>
@@ -25777,14 +24043,10 @@
         <v>93.776669999999996</v>
       </c>
       <c r="Q197" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S197" t="str">
-        <f t="shared" si="3"/>
-        <v>2016-Q2</v>
-      </c>
-    </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>42491</v>
       </c>
@@ -25830,12 +24092,8 @@
       <c r="Q198" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S198" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>42522</v>
       </c>
@@ -25881,12 +24139,8 @@
       <c r="Q199" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S199" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="200" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>42552</v>
       </c>
@@ -25930,14 +24184,10 @@
         <v>95.169089999999997</v>
       </c>
       <c r="Q200" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S200" t="str">
-        <f t="shared" si="3"/>
-        <v>2016-Q3</v>
-      </c>
-    </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>42583</v>
       </c>
@@ -25983,12 +24233,8 @@
       <c r="Q201" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S201" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="202" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>42614</v>
       </c>
@@ -26032,14 +24278,10 @@
         <v>94.903949999999995</v>
       </c>
       <c r="Q202" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S202" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>42644</v>
       </c>
@@ -26085,12 +24327,8 @@
       <c r="Q203" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S203" t="str">
-        <f t="shared" si="3"/>
-        <v>2016-Q4</v>
-      </c>
-    </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>42675</v>
       </c>
@@ -26136,12 +24374,8 @@
       <c r="Q204" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S204" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>42705</v>
       </c>
@@ -26187,12 +24421,8 @@
       <c r="Q205" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S205" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="206" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>42736</v>
       </c>
@@ -26238,12 +24468,8 @@
       <c r="Q206" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S206" t="str">
-        <f t="shared" si="3"/>
-        <v>2017-Q1</v>
-      </c>
-    </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>42767</v>
       </c>
@@ -26287,14 +24513,10 @@
         <v>98.084819999999993</v>
       </c>
       <c r="Q207" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S207" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>42795</v>
       </c>
@@ -26338,14 +24560,10 @@
         <v>97.248009999999994</v>
       </c>
       <c r="Q208" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S208" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>42826</v>
       </c>
@@ -26391,12 +24609,8 @@
       <c r="Q209" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S209" t="str">
-        <f t="shared" si="3"/>
-        <v>2017-Q2</v>
-      </c>
-    </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="210" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>42856</v>
       </c>
@@ -26440,14 +24654,10 @@
         <v>96.713660000000004</v>
       </c>
       <c r="Q210" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="S210" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>42887</v>
       </c>
@@ -26491,14 +24701,10 @@
         <v>95.978059999999999</v>
       </c>
       <c r="Q211" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S211" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>42917</v>
       </c>
@@ -26544,12 +24750,8 @@
       <c r="Q212" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S212" t="str">
-        <f t="shared" si="3"/>
-        <v>2017-Q3</v>
-      </c>
-    </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="213" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>42948</v>
       </c>
@@ -26595,12 +24797,8 @@
       <c r="Q213" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S213" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="214" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>42979</v>
       </c>
@@ -26644,14 +24842,10 @@
         <v>97.147959999999998</v>
       </c>
       <c r="Q214" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S214" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>43009</v>
       </c>
@@ -26697,12 +24891,8 @@
       <c r="Q215" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S215" t="str">
-        <f t="shared" si="3"/>
-        <v>2017-Q4</v>
-      </c>
-    </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>43040</v>
       </c>
@@ -26748,12 +24938,8 @@
       <c r="Q216" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S216" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>43070</v>
       </c>
@@ -26799,12 +24985,8 @@
       <c r="Q217" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S217" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>43101</v>
       </c>
@@ -26850,12 +25032,8 @@
       <c r="Q218" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S218" t="str">
-        <f t="shared" si="3"/>
-        <v>2018-Q1</v>
-      </c>
-    </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>43132</v>
       </c>
@@ -26899,14 +25077,10 @@
         <v>98.215770000000006</v>
       </c>
       <c r="Q219" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S219" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>43160</v>
       </c>
@@ -26952,12 +25126,8 @@
       <c r="Q220" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S220" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>43191</v>
       </c>
@@ -27003,12 +25173,8 @@
       <c r="Q221" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S221" t="str">
-        <f t="shared" si="3"/>
-        <v>2018-Q2</v>
-      </c>
-    </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="222" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>43221</v>
       </c>
@@ -27054,12 +25220,8 @@
       <c r="Q222" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S222" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="223" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>43252</v>
       </c>
@@ -27105,12 +25267,8 @@
       <c r="Q223" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S223" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="224" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>43282</v>
       </c>
@@ -27156,12 +25314,8 @@
       <c r="Q224" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S224" t="str">
-        <f t="shared" si="3"/>
-        <v>2018-Q3</v>
-      </c>
-    </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="225" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>43313</v>
       </c>
@@ -27205,14 +25359,10 @@
         <v>102.39279999999999</v>
       </c>
       <c r="Q225" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S225" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="226" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>43344</v>
       </c>
@@ -27258,12 +25408,8 @@
       <c r="Q226" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S226" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="227" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>43374</v>
       </c>
@@ -27309,12 +25455,8 @@
       <c r="Q227" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S227" t="str">
-        <f t="shared" si="3"/>
-        <v>2018-Q4</v>
-      </c>
-    </row>
-    <row r="228" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="228" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>43405</v>
       </c>
@@ -27358,14 +25500,10 @@
         <v>106.9331</v>
       </c>
       <c r="Q228" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S228" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="229" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>43435</v>
       </c>
@@ -27411,12 +25549,8 @@
       <c r="Q229" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S229" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="230" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>43466</v>
       </c>
@@ -27460,14 +25594,10 @@
         <v>100.9444</v>
       </c>
       <c r="Q230" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S230" t="str">
-        <f t="shared" si="3"/>
-        <v>2019-Q1</v>
-      </c>
-    </row>
-    <row r="231" spans="1:19" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>43497</v>
       </c>
@@ -27513,12 +25643,8 @@
       <c r="Q231" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S231" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="232" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="232" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>43525</v>
       </c>
@@ -27564,12 +25690,8 @@
       <c r="Q232" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S232" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="233" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="233" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>43556</v>
       </c>
@@ -27615,12 +25737,8 @@
       <c r="Q233" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S233" t="str">
-        <f t="shared" si="3"/>
-        <v>2019-Q2</v>
-      </c>
-    </row>
-    <row r="234" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="234" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>43586</v>
       </c>
@@ -27666,12 +25784,8 @@
       <c r="Q234" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S234" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="235" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>43617</v>
       </c>
@@ -27717,12 +25831,8 @@
       <c r="Q235" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S235" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="236" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>43647</v>
       </c>
@@ -27766,14 +25876,10 @@
         <v>104.0864</v>
       </c>
       <c r="Q236" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S236" t="str">
-        <f t="shared" si="3"/>
-        <v>2019-Q3</v>
-      </c>
-    </row>
-    <row r="237" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="237" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>43678</v>
       </c>
@@ -27819,12 +25925,8 @@
       <c r="Q237" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S237" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="238" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>43709</v>
       </c>
@@ -27870,12 +25972,8 @@
       <c r="Q238" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S238" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="239" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>43739</v>
       </c>
@@ -27921,12 +26019,8 @@
       <c r="Q239" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S239" t="str">
-        <f t="shared" si="3"/>
-        <v>2019-Q4</v>
-      </c>
-    </row>
-    <row r="240" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="240" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>43770</v>
       </c>
@@ -27972,12 +26066,8 @@
       <c r="Q240" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S240" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="241" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="241" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>43800</v>
       </c>
@@ -28023,12 +26113,8 @@
       <c r="Q241" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S241" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="242" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>43831</v>
       </c>
@@ -28072,14 +26158,10 @@
         <v>104.4068</v>
       </c>
       <c r="Q242" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S242" t="str">
-        <f t="shared" si="3"/>
-        <v>2020-Q1</v>
-      </c>
-    </row>
-    <row r="243" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="243" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>43862</v>
       </c>
@@ -28125,12 +26207,8 @@
       <c r="Q243" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S243" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="244" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>43891</v>
       </c>
@@ -28176,12 +26254,8 @@
       <c r="Q244" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S244" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="245" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>43922</v>
       </c>
@@ -28227,12 +26301,8 @@
       <c r="Q245" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S245" t="str">
-        <f t="shared" si="3"/>
-        <v>2020-Q2</v>
-      </c>
-    </row>
-    <row r="246" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="246" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>43952</v>
       </c>
@@ -28278,12 +26348,8 @@
       <c r="Q246" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S246" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="247" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>43983</v>
       </c>
@@ -28327,14 +26393,10 @@
         <v>98.343919999999997</v>
       </c>
       <c r="Q247" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S247" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="248" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>44013</v>
       </c>
@@ -28380,12 +26442,8 @@
       <c r="Q248" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S248" t="str">
-        <f t="shared" si="3"/>
-        <v>2020-Q3</v>
-      </c>
-    </row>
-    <row r="249" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="249" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>44044</v>
       </c>
@@ -28431,12 +26489,8 @@
       <c r="Q249" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S249" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="250" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>44075</v>
       </c>
@@ -28482,12 +26536,8 @@
       <c r="Q250" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S250" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="251" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>44105</v>
       </c>
@@ -28533,12 +26583,8 @@
       <c r="Q251" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S251" t="str">
-        <f t="shared" si="3"/>
-        <v>2020-Q4</v>
-      </c>
-    </row>
-    <row r="252" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="252" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>44136</v>
       </c>
@@ -28582,14 +26628,10 @@
         <v>95.814880000000002</v>
       </c>
       <c r="Q252" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S252" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="253" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="253" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>44166</v>
       </c>
@@ -28635,12 +26677,8 @@
       <c r="Q253" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S253" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="254" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>44197</v>
       </c>
@@ -28684,14 +26722,10 @@
         <v>102.5399</v>
       </c>
       <c r="Q254" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S254" t="str">
-        <f t="shared" si="3"/>
-        <v>2021-Q1</v>
-      </c>
-    </row>
-    <row r="255" spans="1:19" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="255" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>44228</v>
       </c>
@@ -28737,12 +26771,8 @@
       <c r="Q255" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S255" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="256" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="256" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>44256</v>
       </c>
@@ -28788,12 +26818,8 @@
       <c r="Q256" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S256" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="257" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="257" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>44287</v>
       </c>
@@ -28839,12 +26865,8 @@
       <c r="Q257" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S257" t="str">
-        <f t="shared" si="3"/>
-        <v>2021-Q2</v>
-      </c>
-    </row>
-    <row r="258" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="258" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>44317</v>
       </c>
@@ -28890,12 +26912,8 @@
       <c r="Q258" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S258" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="259" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>44348</v>
       </c>
@@ -28941,12 +26959,8 @@
       <c r="Q259" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S259" t="str">
-        <f t="shared" ref="S259:S313" si="4">IF(MONTH($A259) = 1, YEAR($A259)&amp;"-Q"&amp;MONTH($A259), IF(MONTH($A259) = 4, YEAR($A259)&amp;"-Q2", IF(MONTH($A259) = 7, YEAR($A259)&amp;"-Q3", IF(MONTH($A259) = 10, YEAR($A259)&amp;"-Q4",""))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="260" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>44378</v>
       </c>
@@ -28992,12 +27006,8 @@
       <c r="Q260" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S260" t="str">
-        <f t="shared" si="4"/>
-        <v>2021-Q3</v>
-      </c>
-    </row>
-    <row r="261" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="261" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>44409</v>
       </c>
@@ -29043,12 +27053,8 @@
       <c r="Q261" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S261" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="262" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>44440</v>
       </c>
@@ -29094,12 +27100,8 @@
       <c r="Q262" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S262" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="263" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="263" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>44470</v>
       </c>
@@ -29145,12 +27147,8 @@
       <c r="Q263" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S263" t="str">
-        <f t="shared" si="4"/>
-        <v>2021-Q4</v>
-      </c>
-    </row>
-    <row r="264" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="264" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>44501</v>
       </c>
@@ -29194,14 +27192,10 @@
         <v>117.0548</v>
       </c>
       <c r="Q264" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S264" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="265" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="265" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>44531</v>
       </c>
@@ -29245,14 +27239,10 @@
         <v>114.967</v>
       </c>
       <c r="Q265" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S265" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="266" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="266" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>44562</v>
       </c>
@@ -29298,12 +27288,8 @@
       <c r="Q266" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S266" t="str">
-        <f t="shared" si="4"/>
-        <v>2022-Q1</v>
-      </c>
-    </row>
-    <row r="267" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="267" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>44593</v>
       </c>
@@ -29349,12 +27335,8 @@
       <c r="Q267" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S267" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="268" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="268" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>44621</v>
       </c>
@@ -29400,12 +27382,8 @@
       <c r="Q268" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S268" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="269" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="269" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>44652</v>
       </c>
@@ -29451,12 +27429,8 @@
       <c r="Q269" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S269" t="str">
-        <f t="shared" si="4"/>
-        <v>2022-Q2</v>
-      </c>
-    </row>
-    <row r="270" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="270" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>44682</v>
       </c>
@@ -29502,12 +27476,8 @@
       <c r="Q270" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S270" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="271" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="271" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>44713</v>
       </c>
@@ -29553,12 +27523,8 @@
       <c r="Q271" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S271" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="272" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="272" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>44743</v>
       </c>
@@ -29604,12 +27570,8 @@
       <c r="Q272" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S272" t="str">
-        <f t="shared" si="4"/>
-        <v>2022-Q3</v>
-      </c>
-    </row>
-    <row r="273" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="273" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>44774</v>
       </c>
@@ -29655,12 +27617,8 @@
       <c r="Q273" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S273" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="274" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>44805</v>
       </c>
@@ -29706,12 +27664,8 @@
       <c r="Q274" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S274" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="275" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="275" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>44835</v>
       </c>
@@ -29755,14 +27709,10 @@
         <v>156.13669999999999</v>
       </c>
       <c r="Q275" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S275" t="str">
-        <f t="shared" si="4"/>
-        <v>2022-Q4</v>
-      </c>
-    </row>
-    <row r="276" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="276" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>44866</v>
       </c>
@@ -29806,14 +27756,10 @@
         <v>155.24549999999999</v>
       </c>
       <c r="Q276" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S276" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="277" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="277" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>44896</v>
       </c>
@@ -29859,12 +27805,8 @@
       <c r="Q277" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S277" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="278" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="278" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>44927</v>
       </c>
@@ -29890,7 +27832,7 @@
         <v>32.5</v>
       </c>
       <c r="I278" s="4">
-        <v>0.89714431762695313</v>
+        <v>0.89714431762695312</v>
       </c>
       <c r="L278">
         <v>99.2</v>
@@ -29910,12 +27852,8 @@
       <c r="Q278" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S278" t="str">
-        <f t="shared" si="4"/>
-        <v>2023-Q1</v>
-      </c>
-    </row>
-    <row r="279" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="279" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>44958</v>
       </c>
@@ -29959,14 +27897,10 @@
         <v>151.26750000000001</v>
       </c>
       <c r="Q279" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S279" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="280" spans="1:19" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="280" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>44986</v>
       </c>
@@ -30012,12 +27946,8 @@
       <c r="Q280" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S280" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="281" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="281" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>45017</v>
       </c>
@@ -30061,14 +27991,10 @@
         <v>152.30090000000001</v>
       </c>
       <c r="Q281" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S281" t="str">
-        <f t="shared" si="4"/>
-        <v>2023-Q2</v>
-      </c>
-    </row>
-    <row r="282" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="282" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>45047</v>
       </c>
@@ -30114,12 +28040,8 @@
       <c r="Q282" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S282" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="283" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>45078</v>
       </c>
@@ -30165,12 +28087,8 @@
       <c r="Q283" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S283" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="284" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>45108</v>
       </c>
@@ -30216,12 +28134,8 @@
       <c r="Q284" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S284" t="str">
-        <f t="shared" si="4"/>
-        <v>2023-Q3</v>
-      </c>
-    </row>
-    <row r="285" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="285" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>45139</v>
       </c>
@@ -30267,12 +28181,8 @@
       <c r="Q285" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S285" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="286" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="286" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>45170</v>
       </c>
@@ -30316,14 +28226,10 @@
         <v>154.00710000000001</v>
       </c>
       <c r="Q286" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S286" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="287" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="287" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>45200</v>
       </c>
@@ -30367,14 +28273,10 @@
         <v>151.3518</v>
       </c>
       <c r="Q287" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S287" t="str">
-        <f t="shared" si="4"/>
-        <v>2023-Q4</v>
-      </c>
-    </row>
-    <row r="288" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="288" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>45231</v>
       </c>
@@ -30420,12 +28322,8 @@
       <c r="Q288" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S288" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="289" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="289" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>45261</v>
       </c>
@@ -30471,12 +28369,8 @@
       <c r="Q289" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S289" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="290" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="290" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>45292</v>
       </c>
@@ -30522,12 +28416,8 @@
       <c r="Q290" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S290" t="str">
-        <f t="shared" si="4"/>
-        <v>2024-Q1</v>
-      </c>
-    </row>
-    <row r="291" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="291" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>45323</v>
       </c>
@@ -30573,12 +28463,8 @@
       <c r="Q291" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S291" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="292" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="292" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>45352</v>
       </c>
@@ -30622,14 +28508,10 @@
         <v>147.32560000000001</v>
       </c>
       <c r="Q292" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S292" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="293" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="293" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>45383</v>
       </c>
@@ -30675,12 +28557,8 @@
       <c r="Q293" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S293" t="str">
-        <f t="shared" si="4"/>
-        <v>2024-Q2</v>
-      </c>
-    </row>
-    <row r="294" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="294" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>45413</v>
       </c>
@@ -30726,12 +28604,8 @@
       <c r="Q294" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S294" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="295" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="295" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>45444</v>
       </c>
@@ -30777,12 +28651,8 @@
       <c r="Q295" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S295" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="296" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="296" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>45474</v>
       </c>
@@ -30828,12 +28698,8 @@
       <c r="Q296" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S296" t="str">
-        <f t="shared" si="4"/>
-        <v>2024-Q3</v>
-      </c>
-    </row>
-    <row r="297" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="297" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>45505</v>
       </c>
@@ -30879,12 +28745,8 @@
       <c r="Q297" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S297" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="298" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>45536</v>
       </c>
@@ -30928,14 +28790,10 @@
         <v>142.3768</v>
       </c>
       <c r="Q298" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S298" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="299" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="299" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>45566</v>
       </c>
@@ -30981,12 +28839,8 @@
       <c r="Q299" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S299" t="str">
-        <f t="shared" si="4"/>
-        <v>2024-Q4</v>
-      </c>
-    </row>
-    <row r="300" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="300" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>45597</v>
       </c>
@@ -31032,12 +28886,8 @@
       <c r="Q300" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S300" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="301" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="301" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>45627</v>
       </c>
@@ -31083,12 +28933,8 @@
       <c r="Q301" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S301" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="302" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="302" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>45658</v>
       </c>
@@ -31134,12 +28980,8 @@
       <c r="Q302" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S302" t="str">
-        <f t="shared" si="4"/>
-        <v>2025-Q1</v>
-      </c>
-    </row>
-    <row r="303" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="303" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>45689</v>
       </c>
@@ -31183,14 +29025,10 @@
         <v>145.47579999999999</v>
       </c>
       <c r="Q303" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S303" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="304" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="304" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>45717</v>
       </c>
@@ -31236,12 +29074,8 @@
       <c r="Q304" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S304" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="305" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="305" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>45748</v>
       </c>
@@ -31284,12 +29118,8 @@
       <c r="Q305" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S305" t="str">
-        <f t="shared" si="4"/>
-        <v>2025-Q2</v>
-      </c>
-    </row>
-    <row r="306" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="306" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>45778</v>
       </c>
@@ -31330,14 +29160,10 @@
         <v>#N/A</v>
       </c>
       <c r="Q306" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S306" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="307" spans="1:19" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="307" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>45809</v>
       </c>
@@ -31380,12 +29206,8 @@
       <c r="Q307" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S307" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="308" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="308" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>45839</v>
       </c>
@@ -31426,14 +29248,10 @@
         <v>#N/A</v>
       </c>
       <c r="Q308" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S308" t="str">
-        <f t="shared" si="4"/>
-        <v>2025-Q3</v>
-      </c>
-    </row>
-    <row r="309" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="309" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>45870</v>
       </c>
@@ -31476,12 +29294,8 @@
       <c r="Q309" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S309" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="310" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="310" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>45901</v>
       </c>
@@ -31522,14 +29336,10 @@
         <v>#N/A</v>
       </c>
       <c r="Q310" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S310" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="311" spans="1:19" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="311" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>45931</v>
       </c>
@@ -31572,12 +29382,8 @@
       <c r="Q311" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S311" t="str">
-        <f t="shared" si="4"/>
-        <v>2025-Q4</v>
-      </c>
-    </row>
-    <row r="312" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="312" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A312" s="1">
         <v>45962</v>
       </c>
@@ -31620,12 +29426,8 @@
       <c r="Q312" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="S312" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="313" spans="1:19" x14ac:dyDescent="0.4">
+    </row>
+    <row r="313" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A313" s="1">
         <v>45992</v>
       </c>
@@ -31667,10 +29469,6 @@
       </c>
       <c r="Q313" s="1" t="e">
         <v>#N/A</v>
-      </c>
-      <c r="S313" t="str">
-        <f t="shared" si="4"/>
-        <v/>
       </c>
     </row>
   </sheetData>
